--- a/figures/parallel_verses/sidrac-teesteye.xlsx
+++ b/figures/parallel_verses/sidrac-teesteye.xlsx
@@ -512,7 +512,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.1903617045322127</v>
+        <v>0.1863493623755582</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>0.3656507273479911</v>
+        <v>0.3582918172473394</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>0.3725223500692627</v>
+        <v>0.3703175877332958</v>
       </c>
     </row>
     <row r="5">
@@ -632,7 +632,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.3987772615659957</v>
+        <v>0.3884632286082695</v>
       </c>
     </row>
     <row r="6">
@@ -672,7 +672,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.422558501092715</v>
+        <v>0.4152750711419589</v>
       </c>
     </row>
     <row r="7">
@@ -712,31 +712,31 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.4482630576489262</v>
+        <v>0.443842576564125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verre van mi wille werpen / Al in die stat tAntwerpen</t>
+          <t>Doen ic dit werc ierst began / Ende hebbe versleten nochtan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AL tote Andwerpen in die stat / Luste tween ghesellen dat</t>
+          <t>Doen kerstenheyt yrst began / Die keyser ende de heren nochtan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ver van ik willen werpen / al in die stad te antwerpen</t>
+          <t>toen ik dit werk eerst beginnen / en hebben verslijten nochtan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>al tot antwerpen in die stad / lust twee gezel dat</t>
+          <t>toen kerstenheid eerst beginnen / die keizer en de heer nochtan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -752,7 +752,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.452782102568219</v>
+        <v>0.4487878640357946</v>
       </c>
     </row>
     <row r="9">
@@ -766,7 +766,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alle die hemele ende die eerde / Ende daer boven die hoghe trone</t>
+          <t>Ende daer boven die hoghe trone / Die hi al vulde scone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>al die hemel en die aarde / en daar boven die hoog troon</t>
+          <t>en daar boven die hoog troon / die hij al vullen schoon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -792,31 +792,31 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.4553179785743693</v>
+        <v>0.450028803365246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>28</v>
+        <v>208</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Die de dinc te rechte besiet / Die den tijt onledich maken</t>
+          <t>Verre van mi wille werpen / Al in die stat tAntwerpen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Want die de dinc te rechte besiet / So en was Cristus leven anders niet</t>
+          <t>AL tote Andwerpen in die stat / Luste tween ghesellen dat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>die de ding te rechte bezien / die de tijd onledig maken</t>
+          <t>ver van ik willen werpen / al in die stad te antwerpen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>want die de ding te rechte bezien / zo ne zijn NOU-P leven anders niet</t>
+          <t>al tot antwerpen in die stad / lust twee gezel dat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -832,31 +832,31 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0.4563644132005811</v>
+        <v>0.451927146493654</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Doen ic dit werc ierst began / Ende hebbe versleten nochtan</t>
+          <t>Die de dinc te rechte besiet / Die den tijt onledich maken</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Doen kerstenheyt yrst began / Die keyser ende de heren nochtan</t>
+          <t>Want die de dinc te rechte besiet / So en was Cristus leven anders niet</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>toen ik dit werk eerst beginnen / en hebben verslijten nochtan</t>
+          <t>die de ding te rechte bezien / die de tijd onledig maken</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>toen kerstenheid eerst beginnen / die keizer en de heer nochtan</t>
+          <t>want die de ding te rechte bezien / zo ne zijn NOU-P leven anders niet</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -872,31 +872,31 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0.458654119547394</v>
+        <v>0.4523333571927933</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Beide die heilege Geest ende die Sone / Die een God sijn metten Vader</t>
+          <t>Daer by sy es ghevoeget scone / Daer boven inden oversten trone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Des onne ons ende gheve sijn volleest / Die Vader die Sone die Heilighe Gheest</t>
+          <t>Ende daer boven die hoghe trone / Die hi al vulde scone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>beide die heilig geest en die zoon / die een god zijn met de vader</t>
+          <t>daar bij zij zijn voegen schoon / daar boven in de overst troon</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>de on ons en geven zijn volleest / die vader die zoon die heilig geest</t>
+          <t>en daar boven die hoog troon / die hij al vullen schoon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -912,31 +912,31 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>0.4617508968247759</v>
+        <v>0.453196439562612</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Daer by sy es ghevoeget scone / Daer boven inden oversten trone</t>
+          <t>Die dese vrouwe niet en mint / Die de Vader alsoe minde</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ende daer boven die hoghe trone / Die hi al vulde scone</t>
+          <t>Om dat die vader deen kint / Meer dan hen hadde ghemint</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>daar bij zij zijn voegen schoon / daar boven in de overst troon</t>
+          <t>die deze vrouwe niet ne minnen / die de vader alzo minnen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>en daar boven die hoog troon / die hij al vullen schoon</t>
+          <t>om dat die vader de een kind / meer dan zij hebben minnen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -952,31 +952,31 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.4635471018536821</v>
+        <v>0.4594762129113749</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Die dese vrouwe niet en mint / Die de Vader alsoe minde</t>
+          <t>Als God de warelt zal domen / Ende hoe si ter bliscap sullen comen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Om dat die vader deen kint / Meer dan hen hadde ghemint</t>
+          <t>Ende sal ten ionxten daghe comen / Alle mensche doemen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>die deze vrouwe niet ne minnen / die de vader alzo minnen</t>
+          <t>als NOU-P de wereld zullen doemen / en hoe zij ter blijdschap zullen komen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>om dat die vader de een kind / meer dan zij hebben minnen</t>
+          <t>en zullen ten jong dag komen / al mens doemen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -992,31 +992,31 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.465025414534289</v>
+        <v>0.4599579608065072</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dat overlijt soe cortelike / Verdienen souden hemelrike</t>
+          <t>Beide die heilege Geest ende die Sone / Die een God sijn metten Vader</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mach die mensche verdienen des / Dat hemelrike sijn es</t>
+          <t>Des onne ons ende gheve sijn volleest / Die Vader die Sone die Heilighe Gheest</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dat overlijd zo kortelijk / verdienen zullen hemelrijk</t>
+          <t>beide die heilig geest en die zoon / die een god zijn met de vader</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>mogen die mens verdienen de / dat hemelrijk zijn zijn</t>
+          <t>de on ons en geven zijn volleest / die vader die zoon die heilig geest</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1032,31 +1032,31 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.4672535666457324</v>
+        <v>0.4635940150809571</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hondertfout van lone / Te Antwerpen daer ic wone</t>
+          <t>Niet toe gebringen en can / Het es te swaer elcken man</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boendale heetmen mi daer / Ende wone te Andwerpen nu</t>
+          <t>Ende dat es swaer elken man / Dat nieman gheweten en can</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>honderdfout van loon / te NOU-P daar ik wonen</t>
+          <t>niet toegespreken gebrengen ne kunnen / het zijn te zwaar elk man</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NOU-P heten men ik daar / en wonen te NOU-P nu</t>
+          <t>en dat zijn zwaar elk man / dat niemand geweten ne kunnen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1072,31 +1072,31 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>0.4682462333238172</v>
+        <v>0.4644497875635354</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Als God de warelt zal domen / Ende hoe si ter bliscap sullen comen</t>
+          <t>Alst comt te minen laetsten stonden / Dat hi mi dan al mine zonden</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ende sal ten ionxten daghe comen / Alle mensche doemen</t>
+          <t>Dat hi hem huede van sonden / Ende dat hi peynse tallen stonden</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>als NOU-P de wereld zullen doemen / en hoe zij ter blijdschap zullen komen</t>
+          <t>als het komen te mijn laat stond / dat hij ik dan al mijn zonde</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>en zullen ten jong dag komen / al mens doemen</t>
+          <t>dat hij hij houden van zonde / en dat hij peinzen te al stond</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1112,31 +1112,31 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>0.4710128776349679</v>
+        <v>0.4726831029464137</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anders dan dat ic niet en woude / Dat dese edele leringe soude</t>
+          <t>Hondertfout van lone / Te Antwerpen daer ic wone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>So en was Cristus leven anders niet / Dan exemple ende leringhe mede</t>
+          <t>Boendale heetmen mi daer / Ende wone te Andwerpen nu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>anders dan dat ik niet ne willen / dat deze edel lering zullen</t>
+          <t>honderdfout van loon / te NOU-P daar ik wonen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>zo ne zijn NOU-P leven anders niet / dan exempel en lering mede</t>
+          <t>NOU-P heten men ik daar / en wonen te NOU-P nu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1152,31 +1152,31 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>0.4710132586376783</v>
+        <v>0.4731540997647719</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Niet toe gebringen en can / Het es te swaer elcken man</t>
+          <t>Dat overlijt soe cortelike / Verdienen souden hemelrike</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ende dat es swaer elken man / Dat nieman gheweten en can</t>
+          <t>Mach die mensche verdienen des / Dat hemelrike sijn es</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>niet toegespreken gebrengen ne kunnen / het zijn te zwaar elk man</t>
+          <t>dat overlijd zo kortelijk / verdienen zullen hemelrijk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>en dat zijn zwaar elk man / dat niemand geweten ne kunnen</t>
+          <t>mogen die mens verdienen de / dat hemelrijk zijn zijn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,31 +1192,31 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>0.4734291362270281</v>
+        <v>0.4735828741180762</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>4</v>
+        <v>202</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alsoe sijn geesten vanden heren / Van Pertelpeuse van Amedase</t>
+          <t>Ende ic bidde hem allen met trauwen / Die desen bouc selen scauwen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Die van Grieken ende van Cartago / Ende van anderen landen also</t>
+          <t>Ende oec machmen in u scouwen / Meer dogheden ende trouwen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>alzo zijn geest van de heer / van partelpeuze van NOU-P</t>
+          <t>en ik bidden hij al met trouw / die deze boek zullen schouwen</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>die van griek en van NOU-P / en van ander land alzo</t>
+          <t>en ook mogen men in u schouwen / meer deugd en trouw</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1232,31 +1232,31 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>0.4773926678825862</v>
+        <v>0.476460492549992</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Anders dant dauctor ute gaf / Die anders doen sy doen quaet</t>
+          <t>Alsoe sijn geesten vanden heren / Van Pertelpeuse van Amedase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ende die anders segghen daer af / Si doen quaet sijts gewes</t>
+          <t>Die van Grieken ende van Cartago / Ende van anderen landen also</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>anders dan het de autor uiten geven / die anders doen zij doen kwaad</t>
+          <t>alzo zijn geest van de heer / van partelpeuze van NOU-P</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>en die anders zeggen daar af / zij doen kwaad zijn het gewis</t>
+          <t>die van griek en van NOU-P / en van ander land alzo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1272,31 +1272,31 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>0.4826952441391057</v>
+        <v>0.4769287753767837</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alst comt te minen laetsten stonden / Dat hi mi dan al mine zonden</t>
+          <t>Vanden cruden latic uut / Ende vanden stenen die virtuit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dat hi hem huede van sonden / Ende dat hi peynse tallen stonden</t>
+          <t>In haer macht ende in haer virtuut / Maer de twee sijn nu wt</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>als het komen te mijn laat stond / dat hij ik dan al mijn zonde</t>
+          <t>van de kruid laten ik uit / en van de steen die virtuut</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>dat hij hij houden van zonde / en dat hij peinzen te al stond</t>
+          <t>in haar macht en in haar virtuut / maar de twee zijn nu uit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1312,31 +1312,31 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>0.4832956497287483</v>
+        <v>0.4771771433516131</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>202</v>
+        <v>83</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ende ic bidde hem allen met trauwen / Die desen bouc selen scauwen</t>
+          <t>Anders dan dat ic niet en woude / Dat dese edele leringe soude</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ende oec machmen in u scouwen / Meer dogheden ende trouwen</t>
+          <t>So en was Cristus leven anders niet / Dan exemple ende leringhe mede</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>en ik bidden hij al met trouw / die deze boek zullen schouwen</t>
+          <t>anders dan dat ik niet ne willen / dat deze edel lering zullen</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>en ook mogen men in u schouwen / meer deugd en trouw</t>
+          <t>zo ne zijn NOU-P leven anders niet / dan exempel en lering mede</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1352,31 +1352,31 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>0.4883122291141621</v>
+        <v>0.4775498275951144</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vanden cruden latic uut / Ende vanden stenen die virtuit</t>
+          <t>Want dese bouc hevet in / Der warelt fundament ende beghin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>In haer macht ende in haer virtuut / Maer de twee sijn nu wt</t>
+          <t>Soudic u des maken in inne / Vander werelt beghinne</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>van de kruid laten ik uit / en van de steen die virtuut</t>
+          <t>want deze boek hebben in / de wereld fundament en begin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>in haar macht en in haar virtuut / maar de twee zijn nu uit</t>
+          <t>zullen ik u des maken in in / van de wereld begin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1392,31 +1392,31 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>0.4888994988392166</v>
+        <v>0.4856573127009216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Want dese bouc hevet in / Der warelt fundament ende beghin</t>
+          <t>Epiloog / Ghelooft zi God van hemelrike</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Soudic u des maken in inne / Vander werelt beghinne</t>
+          <t>God gheve hem sijn hemelrike / Nu hebdi verstaen die nuthede</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>want deze boek hebben in / de wereld fundament en begin</t>
+          <t>epiloog / loven zij NOU-P van hemelrijk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>zullen ik u des maken in in / van de wereld begin</t>
+          <t>NOU-P geven hij zijn hemelrijk / nu hebben gij verstaan die nutheid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1432,31 +1432,31 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0.4964938066734358</v>
+        <v>0.4892107031586662</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Epiloog / Ghelooft zi God van hemelrike</t>
+          <t>Anders dant dauctor ute gaf / Die anders doen sy doen quaet</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>God gheve hem sijn hemelrike / Nu hebdi verstaen die nuthede</t>
+          <t>Ende die anders segghen daer af / Si doen quaet sijts gewes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>epiloog / loven zij NOU-P van hemelrijk</t>
+          <t>anders dan het de autor uiten geven / die anders doen zij doen kwaad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NOU-P geven hij zijn hemelrijk / nu hebben gij verstaan die nutheid</t>
+          <t>en die anders zeggen daar af / zij doen kwaad zijn het gewis</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1472,7 +1472,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>0.5011749274451229</v>
+        <v>0.4892778759937204</v>
       </c>
     </row>
     <row r="27">
@@ -1512,7 +1512,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>0.5022833270539706</v>
+        <v>0.4920425490496444</v>
       </c>
     </row>
     <row r="28">
@@ -1552,31 +1552,31 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>0.5026519879615747</v>
+        <v>0.500275261817674</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46</v>
+        <v>181</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Te Antwerpen daer ic wone / Soe quam my een boec ter hant</t>
+          <t>Die een God sijn metten Vader / Dus heeft sy algader</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boendale heetmen mi daer / Ende wone te Andwerpen nu</t>
+          <t>Si schinen dat si weten algader / Die verholenheyt des Vader</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>te NOU-P daar ik wonen / zo komen ik een boek ter hand</t>
+          <t>die een god zijn met de vader / dus hebben zij algader</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NOU-P heten men ik daar / en wonen te NOU-P nu</t>
+          <t>zij schijnen dat zij weten algader / die verholenheid de vader</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1592,31 +1592,31 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>0.5057872959756571</v>
+        <v>0.5005578624138319</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Die ic hier na bescrive / Die boec daer icse ute trac</t>
+          <t>Want die tijt es ons ghegeuen / Omme dat wy in dit leven</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dat si wel te verstane gheven / In haren boeken die si hebben bescreven</t>
+          <t>God heeft den man ghegheven / Grote gracie in dit leven</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>die ik hier na beschrijven / die boek daar ik zij uit trekken</t>
+          <t>want die tijd zijn ons geven / om dat wij in dit leven</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>dat zij wel te verstaan geven / in haar boek die zij hebben beschrijven</t>
+          <t>NOU-P hebben de man geven / groot gratie in dit leven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1632,31 +1632,31 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>0.5081805985457799</v>
+        <v>0.5031899640670651</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>181</v>
+        <v>94</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Die een God sijn metten Vader / Dus heeft sy algader</t>
+          <t>Die ic hier na bescrive / Die boec daer icse ute trac</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Si schinen dat si weten algader / Die verholenheyt des Vader</t>
+          <t>Dat si wel te verstane gheven / In haren boeken die si hebben bescreven</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>die een god zijn met de vader / dus hebben zij algader</t>
+          <t>die ik hier na beschrijven / die boek daar ik zij uit trekken</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>zij schijnen dat zij weten algader / die verholenheid de vader</t>
+          <t>dat zij wel te verstaan geven / in haar boek die zij hebben beschrijven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1672,31 +1672,31 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>0.5120894250641275</v>
+        <v>0.505475040091498</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Want die tijt es ons ghegeuen / Omme dat wy in dit leven</t>
+          <t>Te Antwerpen daer ic wone / Soe quam my een boec ter hant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>God heeft den man ghegheven / Grote gracie in dit leven</t>
+          <t>Boendale heetmen mi daer / Ende wone te Andwerpen nu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>want die tijd zijn ons geven / om dat wij in dit leven</t>
+          <t>te NOU-P daar ik wonen / zo komen ik een boek ter hand</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NOU-P hebben de man geven / groot gratie in dit leven</t>
+          <t>NOU-P heten men ik daar / en wonen te NOU-P nu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1712,31 +1712,31 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>0.51413622868467</v>
+        <v>0.5070735042739766</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>29</v>
+        <v>220</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Die den tijt onledich maken / Met onoerboerliken saken</t>
+          <t>Ende na dit leven hemelrike / Amen segt gemeenlike</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Een sake daer hem een man / Onledech mede maken mach</t>
+          <t>Voor Gode te draghene in hemelrike / Ende voor dingle ghemeynlike</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>die de tijd onledig maken / met onoorbaarlijk zaak</t>
+          <t>en na dit leven hemelrijk / amen zeggen gemeenlijk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>een sake daar hij een man / onledig mede maken mogen</t>
+          <t>voor NOU-P te dragen in hemelrijk / en voor dengel gemeenlijk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1752,31 +1752,31 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>0.5208856706166706</v>
+        <v>0.5096253256984862</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>184</v>
+        <v>67</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Daer by eest openbare / Dat haer niet en es ontseit</t>
+          <t>Die de materie sal leggen wale / Van ere tale in een ander tale</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>In dEwangelie openbare / Dat si doen des en doet niet</t>
+          <t>Deen es behendech ende mach wale / Gheven ende can oec wel sijn tale</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>daar bij zijn het openbaar / dat zij niet ne zijn ontzeggen</t>
+          <t>die de materie zullen leggen wel / van een taal in een ander taal</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>in de ewangelie openbaar / dat zij doen de ne doen niet</t>
+          <t>de een zijn behendig en mogen wel / geven en kunnen ook wel zijn taal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1792,7 +1792,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>0.5209772624748621</v>
+        <v>0.5114057073089073</v>
       </c>
     </row>
     <row r="35">
@@ -1832,31 +1832,31 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>0.5213204302180551</v>
+        <v>0.5160438237052525</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ende na dit leven hemelrike / Amen segt gemeenlike</t>
+          <t>Daer by eest openbare / Dat haer niet en es ontseit</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Voor Gode te draghene in hemelrike / Ende voor dingle ghemeynlike</t>
+          <t>Ende saen gheloven si datmen hen seyt / Daer om es den wiven ontseyt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>en na dit leven hemelrijk / amen zeggen gemeenlijk</t>
+          <t>daar bij zijn het openbaar / dat zij niet ne zijn ontzeggen</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>voor NOU-P te dragen in hemelrijk / en voor dengel gemeenlijk</t>
+          <t>en zaan geloven zij dat men zij zeggen / daar om zijn de wijf ontzeggen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1872,31 +1872,31 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>0.522103726154506</v>
+        <v>0.5167431256677042</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Die de materie sal leggen wale / Van ere tale in een ander tale</t>
+          <t>Es geheten die wise Sidrac / Na enen clerc wijs ende fijn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Deen es behendech ende mach wale / Gheven ende can oec wel sijn tale</t>
+          <t>Ende wiese heeft int herte sijn / Dats een recht dorpre fijn</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>die de materie zullen leggen wel / van een taal in een ander taal</t>
+          <t>zijn heten die wijze NOU-P / na een klerk wijs en fijn</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>de een zijn behendig en mogen wel / geven en kunnen ook wel zijn taal</t>
+          <t>en wijs hebben in het hart zijn / dat zijn een recht dorper fijn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1912,31 +1912,31 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>0.5236625274418988</v>
+        <v>0.5172690186291975</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Es geheten die wise Sidrac / Na enen clerc wijs ende fijn</t>
+          <t>Dat in de werelt soude gevallen / Ende hoe sy inden soude met allen</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Es voer Gode also mare / Alse eens clercs des benic wijs</t>
+          <t>So selen si ghelijc met allen / Ane der kerstene wet vallen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>zijn heten die wijze NOU-P / na een klerk wijs en fijn</t>
+          <t>dat in de wereld zullen vallen / en hoe zij innen zullen met al</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>zijn voor NOU-P alzo maar / als een klerk de benig wijs</t>
+          <t>zo zullen zij gelijk met al / aan de kersten wet vallen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1952,31 +1952,31 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>0.5236841992675074</v>
+        <v>0.5203529057785543</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dat in de werelt soude gevallen / Ende hoe sy inden soude met allen</t>
+          <t>Ende de welke behouden zal sijn / Als God de warelt zal domen</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>So selen si ghelijc met allen / Ane der kerstene wet vallen</t>
+          <t>Ende sal ten ionxten daghe comen / Alle mensche doemen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>dat in de wereld zullen vallen / en hoe zij innen zullen met al</t>
+          <t>en de welk behouden zullen zijn / als NOU-P de wereld zullen doemen</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>zo zullen zij gelijk met al / aan de kersten wet vallen</t>
+          <t>en zullen ten jong dag komen / al mens doemen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1992,31 +1992,31 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
-        <v>0.5307086010794029</v>
+        <v>0.5217468489370523</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dat haer niet en es ontseit / Vander edelre Godheit</t>
+          <t>In dichte niet dat weet wale / Dien boec ute altemale</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dat miere herten ghenoech dede / Vander hogher godhede</t>
+          <t>I ziele es beter dat weet wale / Dan dese werelt altemale</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dat zij niet ne zijn ontzeggen / van de edel godheid</t>
+          <t>in dicht niet dat weten wel / dat boek uit altemaal</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>dat mijn hert genoeg doen / van de hoog godheid</t>
+          <t xml:space="preserve"> ziel zijn goed dat weten wel / dan deze wereld altemaal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2032,31 +2032,31 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>0.5312281397029259</v>
+        <v>0.5218827128059875</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ende de welke behouden zal sijn / Als God de warelt zal domen</t>
+          <t>In hore omme die dinc / Dat sire den Sone by ontfinc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ende sal ten ionxten daghe comen / Alle mensche doemen</t>
+          <t>Dat was Christus in waerre dinc / Die menschelike vorme ontfinc</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>en de welk behouden zullen zijn / als NOU-P de wereld zullen doemen</t>
+          <t>in haar om die ding / dat zijn de zoon bij ontvangen</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>en zullen ten jong dag komen / al mens doemen</t>
+          <t>dat zijn NOU-P in waar ding / die menselijk vorm ontvangen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2072,31 +2072,31 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>0.5317309766601233</v>
+        <v>0.5219929484635866</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hoe der inglen coor sijn gheheten / Dit was hem algader cont</t>
+          <t>Die den tijt onledich maken / Met onoerboerliken saken</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hem en es verborghen niet / Het es hem algader cont</t>
+          <t>Want piesters in waerre saken / Den ghenen moghen maken</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>hoe de engel koor zijn heten / dit zijn hij algader kond</t>
+          <t>die de tijd onledig maken / met onoorbaarlijk zaak</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>hij ne zijn verborgen niet / het zijn hij algader kond</t>
+          <t>want piester in waar zaak / de gene mogen maken</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2112,31 +2112,31 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
-        <v>0.532528878496999</v>
+        <v>0.524381343906513</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>In dichte niet dat weet wale / Dien boec ute altemale</t>
+          <t>Dat haer niet en es ontseit / Vander edelre Godheit</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>I ziele es beter dat weet wale / Dan dese werelt altemale</t>
+          <t>Dat miere herten ghenoech dede / Vander hogher godhede</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>in dicht niet dat weten wel / dat boek uit altemaal</t>
+          <t>dat zij niet ne zijn ontzeggen / van de edel godheid</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ziel zijn goed dat weten wel / dan deze wereld altemaal</t>
+          <t>dat mijn hert genoeg doen / van de hoog godheid</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2152,31 +2152,31 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>0.5329121994615758</v>
+        <v>0.5247564093480507</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>In hore omme die dinc / Dat sire den Sone by ontfinc</t>
+          <t>Hoe der inglen coor sijn gheheten / Dit was hem algader cont</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dat was Christus in waerre dinc / Die menschelike vorme ontfinc</t>
+          <t>Hem en es verborghen niet / Het es hem algader cont</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>in haar om die ding / dat zijn de zoon bij ontvangen</t>
+          <t>hoe de engel koor zijn heten / dit zijn hij algader kond</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>dat zijn NOU-P in waar ding / die menselijk vorm ontvangen</t>
+          <t>hij ne zijn verborgen niet / het zijn hij algader kond</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2192,7 +2192,7 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>0.5337740982843791</v>
+        <v>0.5265852770289087</v>
       </c>
     </row>
     <row r="45">
@@ -2232,7 +2232,7 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>0.5392494639673491</v>
+        <v>0.5322540979495354</v>
       </c>
     </row>
     <row r="46">
@@ -2272,31 +2272,31 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>0.5402804584760457</v>
+        <v>0.5340832874134025</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Die hem ane die boeke houden / Daer sy clene profijt inne leren</t>
+          <t>Die drievuldicheit in hare / Daer by eest openbare</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ende Moyses boeke hilden si / Ende propheten oec daer bi</t>
+          <t>Wouter dus sijn openbare / Die gheloven comen hare</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>die hij aan die beuk houden / daar zij klein profijt in leren</t>
+          <t>die drievuldigheid in haar / daar bij zijn het openbaar</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>en NOU-P beuk houden zij / en profeten ook daar bij</t>
+          <t>NOU-P dus zijn openbaar / die geloof komen haar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2312,31 +2312,31 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>0.5435692726157175</v>
+        <v>0.5350143697487983</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Verdienen souden hemelrike / Ende die hier luttel sayen</t>
+          <t>Uten Grixe dat hy conste wale / Ende oec ute Ebreusche tale</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mach die mensche verdienen des / Dat hemelrike sijn es</t>
+          <t>Deen es behendech ende mach wale / Gheven ende can oec wel sijn tale</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>verdienen zullen hemelrijk / en die hier luttel zaaien</t>
+          <t>uit dat griks dat hij kunnen wel / en ook uit Ebreus taal</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>mogen die mens verdienen de / dat hemelrijk zijn zijn</t>
+          <t>de een zijn behendig en mogen wel / geven en kunnen ook wel zijn taal</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2352,31 +2352,31 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>0.5474251513317774</v>
+        <v>0.539509070370132</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Die drievuldicheit in hare / Daer by eest openbare</t>
+          <t>Die de Vader alsoe minde / Dat hy sinen heylegen Geest sinde</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wouter dus sijn openbare / Die gheloven comen hare</t>
+          <t>Diemen te deser werelt mint / Werdt in deser bitterheyt gheint</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>die drievuldigheid in haar / daar bij zijn het openbaar</t>
+          <t>die de vader alzo minnen / dat hij zijn heilig geest einden</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NOU-P dus zijn openbaar / die geloof komen haar</t>
+          <t>die men te deze wereld minnen / worden in deze bitterheid einden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2392,31 +2392,31 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>0.5474324761198801</v>
+        <v>0.5404625818326314</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Uten Grixe dat hy conste wale / Ende oec ute Ebreusche tale</t>
+          <t>Die anders doen sy doen quaet / Hoets hem elc dats mijn raet</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Deen es behendech ende mach wale / Gheven ende can oec wel sijn tale</t>
+          <t>Ende prise goede vrouwen dats mijn raet / Ende oec de ghene die sijn quaet</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>uit dat griks dat hij kunnen wel / en ook uit Ebreus taal</t>
+          <t>die anders doen zij doen kwaad / hoe zij hij elk dat zijn mijn raad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>de een zijn behendig en mogen wel / geven en kunnen ook wel zijn taal</t>
+          <t>en prijzen goed vrouw dat zijn mijn raad / en ook de gene die zijn kwaad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2432,31 +2432,31 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>0.5506393971907795</v>
+        <v>0.5431421002294499</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Die de Vader alsoe minde / Dat hy sinen heylegen Geest sinde</t>
+          <t>Vander edelre Godheit / Daer by sy es ghevoeget scone</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Diemen te deser werelt mint / Werdt in deser bitterheyt gheint</t>
+          <t>Dat miere herten ghenoech dede / Vander hogher godhede</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>die de vader alzo minnen / dat hij zijn heilig geest einden</t>
+          <t>van de edel godheid / daar bij zij zijn voegen schoon</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>die men te deze wereld minnen / worden in deze bitterheid einden</t>
+          <t>dat mijn hert genoeg doen / van de hoog godheid</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2472,31 +2472,31 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>0.5533185136535179</v>
+        <v>0.5459224061105666</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ende staet my in staden / Voer des Vaders Sone van hemelrike</t>
+          <t>Die hem ane die boeke houden / Daer sy clene profijt inne leren</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dat die Gods Sone van hemelrike / In ertrike comen soude</t>
+          <t>Ende Moyses boeke hilden si / Ende propheten oec daer bi</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>en staan ik in stade / voor de vader zoon van hemelrijk</t>
+          <t>die hij aan die beuk houden / daar zij klein profijt in leren</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>dat die God zoon van hemelrijk / in aardrijk komen zullen</t>
+          <t>en NOU-P beuk houden zij / en profeten ook daar bij</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2512,31 +2512,31 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>0.5544982278370313</v>
+        <v>0.5467145667792861</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Die anders doen sy doen quaet / Hoets hem elc dats mijn raet</t>
+          <t>Ende staet my in staden / Voer des Vaders Sone van hemelrike</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ende prise goede vrouwen dats mijn raet / Ende oec de ghene die sijn quaet</t>
+          <t>Dat die Gods Sone van hemelrike / In ertrike comen soude</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>die anders doen zij doen kwaad / hoe zij hij elk dat zijn mijn raad</t>
+          <t>en staan ik in stade / voor de vader zoon van hemelrijk</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>en prijzen goed vrouw dat zijn mijn raad / en ook de gene die zijn kwaad</t>
+          <t>dat die God zoon van hemelrijk / in aardrijk komen zullen</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2552,31 +2552,31 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>0.5546107171233691</v>
+        <v>0.5501323634114976</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vander edelre Godheit / Daer by sy es ghevoeget scone</t>
+          <t>Dat hijt al wiste te voren / Dat in de werelt soude gevallen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dat miere herten ghenoech dede / Vander hogher godhede</t>
+          <t>Die si hadden te voren / Ende vielen in sulken toren</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>van de edel godheid / daar bij zij zijn voegen schoon</t>
+          <t>dat hij het al wissen te voren / dat in de wereld zullen vallen</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>dat mijn hert genoeg doen / van de hoog godheid</t>
+          <t>die zij hebben te voren / en vallen in zulk toren</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2592,31 +2592,31 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>0.5548036505077916</v>
+        <v>0.5502904875040122</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dat hijt al wiste te voren / Dat in de werelt soude gevallen</t>
+          <t>Verdienen souden hemelrike / Ende die hier luttel sayen</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Die si hadden te voren / Ende vielen in sulken toren</t>
+          <t>Mach die mensche verdienen des / Dat hemelrike sijn es</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>dat hij het al wissen te voren / dat in de wereld zullen vallen</t>
+          <t>verdienen zullen hemelrijk / en die hier luttel zaaien</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>die zij hebben te voren / en vallen in zulk toren</t>
+          <t>mogen die mens verdienen de / dat hemelrijk zijn zijn</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2632,31 +2632,31 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>0.5548234493721463</v>
+        <v>0.5521658156835663</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>60</v>
+        <v>157</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Een woert niet woude anders keren / Dant die edele wise clerc</t>
+          <t>Ende oec some ander dinc / Die my int herte niet en ginc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Es voer Gode also mare / Alse eens clercs des benic wijs</t>
+          <t>So souden si in hare dinc / Den wech gaen dien Cristus ghinc</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>een woord niet willen anders keren / dan het die edel wijs klerk</t>
+          <t>en ook som ander ding / die ik in het hart niet ne gaan</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>zijn voor NOU-P alzo maar / als een klerk de benig wijs</t>
+          <t>zo zullen zij in haar ding / de weg gaan dat NOU-P gaan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2672,31 +2672,31 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>0.5577524498015258</v>
+        <v>0.554046164056724</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dit was hem algader cont / Hout voor eenen vont</t>
+          <t>Een woert niet woude anders keren / Dant die edele wise clerc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hem en es verborghen niet / Het es hem algader cont</t>
+          <t>Es voer Gode also mare / Alse eens clercs des benic wijs</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>dit zijn hij algader kond / hout voor een vont</t>
+          <t>een woord niet willen anders keren / dan het die edel wijs klerk</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>hij ne zijn verborgen niet / het zijn hij algader kond</t>
+          <t>zijn voor NOU-P alzo maar / als een klerk de benig wijs</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2712,31 +2712,31 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>0.5625279366333239</v>
+        <v>0.5563307948329599</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Omme dat ic van dier edelre leren / Een woert niet woude anders keren</t>
+          <t>Noch geen Walsch en verstaen / Want ic hope sonder waen</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dat si niet en wouden bekeren / Om der goeder liede leren</t>
+          <t>Die ghi nu hier hebt verstaen / Die coninc David dede sonder waen</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>om dat ik van die edel leer / een woord niet willen anders keren</t>
+          <t>noch geen Waals ne verstaan / want ik hopen zonder waan</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>dat zij niet ne willen bekeren / om de goed lieden leer</t>
+          <t>die gij nu hier hebben verstaan / die koning NOU-P doen zonder waan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2752,31 +2752,31 @@
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>0.5642132097349279</v>
+        <v>0.5568001276144436</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>144</v>
+        <v>7</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Want ic oud was vichtich iaer / Doen ic dit werc ierst began</t>
+          <t>Ende menich boec datmen mint / Daer men luttel orboers in vint</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dus die oude rechten / Dat yrst begonsten dienstknechten</t>
+          <t>Waer om dat tfolc datmen nu vint / Gode also sere niet en mint</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>want ik oud zijn vijftig jaar / toen ik dit werk eerst beginnen</t>
+          <t>en menig boek dat men minnen / daar men luttel oorbaar in vinden</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>dus die oud recht / dat eerst beginnen dienstknecht</t>
+          <t>waar om dat dat volk dat men nu vinden / NOU-P alzo zeer niet ne minnen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2792,31 +2792,31 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>0.5668206061274343</v>
+        <v>0.5585715382697105</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>157</v>
+        <v>63</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ende oec some ander dinc / Die my int herte niet en ginc</t>
+          <t>Want rime alsoe wijt vinden / Doet dicke die materie winden</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>So souden si in hare dinc / Den wech gaen dien Cristus ghinc</t>
+          <t>Hi halet goet daer ment windt / Ende vueret daer mens niet en vindt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>en ook som ander ding / die ik in het hart niet ne gaan</t>
+          <t>want rijm alzo wij het vinden / doen dik die materie winden</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>zo zullen zij in haar ding / de weg gaan dat NOU-P gaan</t>
+          <t>hij halen goed daar men het winden / en voeren daar men dat niet ne vinden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2832,31 +2832,31 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>0.5669349442525291</v>
+        <v>0.5592839617570189</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ende hoe si ter bliscap sullen comen / Metten inglen daer boven</t>
+          <t>Dit was hem algader cont / Hout voor eenen vont</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Es hier boven met Onsen Here / Ende metten heylighen inglen fijn</t>
+          <t>Hem en es verborghen niet / Het es hem algader cont</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>en hoe zij ter blijdschap zullen komen / met de engel daar boven</t>
+          <t>dit zijn hij algader kond / hout voor een vont</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>zijn hier boven met ons heer / en met de heilig engel fijn</t>
+          <t>hij ne zijn verborgen niet / het zijn hij algader kond</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2872,31 +2872,31 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>0.567997566959127</v>
+        <v>0.5597663091537827</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dat hy sinen heylegen Geest sinde / In hore omme die dinc</t>
+          <t>Omme dat ic van dier edelre leren / Een woert niet woude anders keren</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>So dat hi sinen Sone sinde / Hier neder om te keerne</t>
+          <t>Dat si niet en wouden bekeren / Om der goeder liede leren</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dat hij zijn heilig geest einden / in haar om die ding</t>
+          <t>om dat ik van die edel leer / een woord niet willen anders keren</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>zo dat hij zijn zoon einden / hier neder om te keren</t>
+          <t>dat zij niet ne willen bekeren / om de goed lieden leer</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2912,31 +2912,31 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>0.5687535816070171</v>
+        <v>0.5612505371302872</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Noch geen Walsch en verstaen / Want ic hope sonder waen</t>
+          <t>Eenen onghelovighen coninc / Hiet Boctus die hem leerde dese dinc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Die ghi nu hier hebt verstaen / Die coninc David dede sonder waen</t>
+          <t>Weten sprac die coninc / Here sprac Maercolf dese dinc</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>noch geen Waals ne verstaan / want ik hopen zonder waan</t>
+          <t>een ongelovig koning / heten NOU-P die hij leren deze ding</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>die gij nu hier hebben verstaan / die koning NOU-P doen zonder waan</t>
+          <t>weten spreken die koning / heer spreken NOU-P deze ding</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2952,31 +2952,31 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
-        <v>0.5689564277124928</v>
+        <v>0.5625552879261153</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>7</v>
+        <v>176</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ende menich boec datmen mint / Daer men luttel orboers in vint</t>
+          <t>Dat hy sinen heylegen Geest sinde / In hore omme die dinc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Waer om dat tfolc datmen nu vint / Gode also sere niet en mint</t>
+          <t>So dat hi sinen Sone sinde / Hier neder om te keerne</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>en menig boek dat men minnen / daar men luttel oorbaar in vinden</t>
+          <t>dat hij zijn heilig geest einden / in haar om die ding</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>waar om dat dat volk dat men nu vinden / NOU-P alzo zeer niet ne minnen</t>
+          <t>zo dat hij zijn zoon einden / hier neder om te keren</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2992,31 +2992,31 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>0.569985014219926</v>
+        <v>0.562836498225905</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dan omme gemene zalichede / Al der goonre dieze lezen</t>
+          <t>Ende hoe sy inden soude met allen / Van firmamenten ende van planeten</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Den mensche tallen steden / Nader zielen salicheden</t>
+          <t>Want si mochtent merken ende weten / Aen delemente ende aen de planeten</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>dan om gemeen zaligheid / al de gonder die zij lezen</t>
+          <t>en hoe zij innen zullen met al / van firmament en van planeet</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>de mens te al stad / na de ziel zaligheid</t>
+          <t>want zij mogen het merken en weten / aan delement en aan de planeet</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3032,31 +3032,31 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>0.5714104956664827</v>
+        <v>0.5631206801220687</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ende hoe die mensce soude leven / Dit boec was in Walsche bescreven</t>
+          <t>Hoet metten achtersten zal gaen / Daer de warelt zal nemen fijn</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dat si wel te verstane gheven / In haren boeken die si hebben bescreven</t>
+          <t>Den wech gaen dien Cristus ghinc / Ende leyden sijn leven fijn</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>en hoe die mens zullen leven / dit boek zijn in Waals beschrijven</t>
+          <t>hoe het met de achterste zullen gaan / daar de wereld zullen nemen fijn</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>dat zij wel te verstaan geven / in haar boek die zij hebben beschrijven</t>
+          <t>de weg gaan dat NOU-P gaan / en leiden zijn leven fijn</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3072,31 +3072,31 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>0.5721073810596012</v>
+        <v>0.5637409627950576</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Want rime alsoe wijt vinden / Doet dicke die materie winden</t>
+          <t>Ende vanden stenen die virtuit / Ende oec eenderhande sotterie</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hi halet goet daer ment windt / Ende vueret daer mens niet en vindt</t>
+          <t>In haer macht ende in haer virtuut / Maer de twee sijn nu wt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>want rijm alzo wij het vinden / doen dik die materie winden</t>
+          <t>en van de steen die virtuut / en ook enerhande zotterij</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>hij halen goed daar men het winden / en voeren daar men dat niet ne vinden</t>
+          <t>in haar macht en in haar virtuut / maar de twee zijn nu uit</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3112,31 +3112,31 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>0.5721379318509854</v>
+        <v>0.5645049818306358</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ende hoe sy inden soude met allen / Van firmamenten ende van planeten</t>
+          <t>Dan omme gemene zalichede / Al der goonre dieze lezen</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Want si mochtent merken ende weten / Aen delemente ende aen de planeten</t>
+          <t>Den mensche tallen steden / Nader zielen salicheden</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>en hoe zij innen zullen met al / van firmament en van planeet</t>
+          <t>dan om gemeen zaligheid / al de gonder die zij lezen</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>want zij mogen het merken en weten / aan delement en aan de planeet</t>
+          <t>de mens te al stad / na de ziel zaligheid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3152,31 +3152,31 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>0.5726434260614814</v>
+        <v>0.5657853816488254</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eenen onghelovighen coninc / Hiet Boctus die hem leerde dese dinc</t>
+          <t>Ende die selve Sone es God / Seker hy es herde sot</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Weten sprac die coninc / Here sprac Maercolf dese dinc</t>
+          <t>Dus at dien appel die sot / Om dat hi waende sijn als God</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>een ongelovig koning / heten NOU-P die hij leren deze ding</t>
+          <t>en die zelf zoon zijn NOU-P / zeker hij zijn hard zot</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>weten spreken die koning / heer spreken NOU-P deze ding</t>
+          <t>dus eten dat appel die zot / om dat hij wanen zijn als NOU-P</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3192,31 +3192,31 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>0.5740237306858682</v>
+        <v>0.5663616052260447</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ende vanden stenen die virtuit / Ende oec eenderhande sotterie</t>
+          <t>Ende hoe die mensce soude leven / Dit boec was in Walsche bescreven</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>In haer macht ende in haer virtuut / Maer de twee sijn nu wt</t>
+          <t>Dat si wel te verstane gheven / In haren boeken die si hebben bescreven</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>en van de steen die virtuut / en ook enerhande zotterij</t>
+          <t>en hoe die mens zullen leven / dit boek zijn in Waals beschrijven</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>in haar macht en in haar virtuut / maar de twee zijn nu uit</t>
+          <t>dat zij wel te verstaan geven / in haar boek die zij hebben beschrijven</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3232,31 +3232,31 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>0.5750424670111508</v>
+        <v>0.5671202635867121</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Beide ter zielen ende ten live / Die ic hier na bescrive</t>
+          <t>Want ic oud was vichtich iaer / Doen ic dit werc ierst began</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alsic u hier na sal bescriven / Op dat ghijt wel verstaen wilt</t>
+          <t>Dus die oude rechten / Dat yrst begonsten dienstknechten</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>beide ter ziel en ten lijf / die ik hier na beschrijven</t>
+          <t>want ik oud zijn vijftig jaar / toen ik dit werk eerst beginnen</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>als ik u hier na zullen beschrijven / op dat gij het wel verstaan willen</t>
+          <t>dus die oud recht / dat eerst beginnen dienstknecht</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3272,31 +3272,31 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
-        <v>0.5753235809271671</v>
+        <v>0.5695159704763194</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hoet metten achtersten zal gaen / Daer de warelt zal nemen fijn</t>
+          <t>Beide ter zielen ende ten live / Die ic hier na bescrive</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Den wech gaen dien Cristus ghinc / Ende leyden sijn leven fijn</t>
+          <t>Alsic u hier na sal bescriven / Op dat ghijt wel verstaen wilt</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>hoe het met de achterste zullen gaan / daar de wereld zullen nemen fijn</t>
+          <t>beide ter ziel en ten lijf / die ik hier na beschrijven</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>de weg gaan dat NOU-P gaan / en leiden zijn leven fijn</t>
+          <t>als ik u hier na zullen beschrijven / op dat gij het wel verstaan willen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3312,31 +3312,31 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
-        <v>0.5767120315709956</v>
+        <v>0.570162415135496</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>171</v>
+        <v>118</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ende die selve Sone es God / Seker hy es herde sot</t>
+          <t>Ende hoe si ter bliscap sullen comen / Metten inglen daer boven</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dus at dien appel die sot / Om dat hi waende sijn als God</t>
+          <t>Es hier boven met Onsen Here / Ende metten heylighen inglen fijn</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>en die zelf zoon zijn NOU-P / zeker hij zijn hard zot</t>
+          <t>en hoe zij ter blijdschap zullen komen / met de engel daar boven</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>dus eten dat appel die zot / om dat hij wanen zijn als NOU-P</t>
+          <t>zijn hier boven met ons heer / en met de heilig engel fijn</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3352,7 +3352,7 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
-        <v>0.5787797815509732</v>
+        <v>0.5717258996399226</v>
       </c>
     </row>
     <row r="74">
@@ -3392,31 +3392,31 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>0.582410246734987</v>
+        <v>0.5728523704710782</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Die desen bouc selen scauwen / Dat sij Gode bidden vor mi</t>
+          <t>Dat hi ons geve sine vrede / Ende sine helige minne mede</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Desen boec sal ic hem senden / Ende hi sal heten Ians Teesteye</t>
+          <t>Ende es altoes eersam mede / Gherne so houdt si in vreden</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>die deze boek zullen schouwen / dat zij NOU-P bidden voor ik</t>
+          <t>dat hij ons geven zijn vrede / en zijn heilig minne mede</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>deze boek zullen ik hij zenden / en hij zullen heten NOU-P teestei</t>
+          <t>en zijn altoos eerzaam mede / gaarne zo houden zij in vrede</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3432,31 +3432,31 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
-        <v>0.5837492462495846</v>
+        <v>0.5747860452724448</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>16</v>
+        <v>204</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Daer men wijsheit doget ende goet / Ende troest van allen goeden rade</t>
+          <t>Dat sij Gode bidden vor mi / Dat hi mijns genadich sij</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>De goede vrouwe es dicke vroet / Haer raet die es gherne goet</t>
+          <t>Ic bids u berechtes mie / Wouter wel lieve veynoet</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>daar men wijsheid doen en goed / en troosten van al goed raad</t>
+          <t>dat zij NOU-P bidden voor ik / dat hij ik genadig zijn</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>de goed vrouwe zijn dik vroed / haar raad die zijn gaarne goed</t>
+          <t>ik bidden dat u berecht ik / NOU-P wel lief veinood</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3472,31 +3472,31 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
-        <v>0.5852563078707045</v>
+        <v>0.5781146174837308</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>178</v>
+        <v>16</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dat sire den Sone by ontfinc / Dus quamen in hare scone</t>
+          <t>Daer men wijsheit doget ende goet / Ende troest van allen goeden rade</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ende dat Karels voerdren scone / Quamen toter vrancscher crone</t>
+          <t>De goede vrouwe es dicke vroet / Haer raet die es gherne goet</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>dat zijn de zoon bij ontvangen / dus komen in haar scone</t>
+          <t>daar men wijsheid doen en goed / en troosten van al goed raad</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>en dat NOU-P vorder scone / komen tot de Franks kroon</t>
+          <t>de goed vrouwe zijn dik vroed / haar raad die zijn gaarne goed</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3512,31 +3512,31 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
-        <v>0.5857294571787988</v>
+        <v>0.5797316867292439</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>61</v>
+        <v>219</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dant die edele wise clerc / Selve dichte in sijn werc</t>
+          <t>Ende sine helige minne mede / Ende na dit leven hemelrike</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Es voer Gode also mare / Alse eens clercs des benic wijs</t>
+          <t>Dien God maecte van hemelrike / Daermen die werelt meerret mede</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>dan het die edel wijs klerk / zelf dichten in zijn werk</t>
+          <t>en zijn heilig minne mede / en na dit leven hemelrijk</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>zijn voor NOU-P alzo maar / als een klerk de benig wijs</t>
+          <t>dat NOU-P maken van hemelrijk / daar men die wereld meren mede</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3552,31 +3552,31 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>0.5859517587385061</v>
+        <v>0.5804191235519147</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dat sij Gode bidden vor mi / Dat hi mijns genadich sij</t>
+          <t>Dat sire den Sone by ontfinc / Dus quamen in hare scone</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ic bids u berechtes mie / Wouter wel lieve veynoet</t>
+          <t>Ende dat Karels voerdren scone / Quamen toter vrancscher crone</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>dat zij NOU-P bidden voor ik / dat hij ik genadig zijn</t>
+          <t>dat zijn de zoon bij ontvangen / dus komen in haar scone</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ik bidden dat u berecht ik / NOU-P wel lief veinood</t>
+          <t>en dat NOU-P vorder scone / komen tot de Franks kroon</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3592,31 +3592,31 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
-        <v>0.5865710118058984</v>
+        <v>0.5804489847290202</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>219</v>
+        <v>80</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ende sine helige minne mede / Ende na dit leven hemelrike</t>
+          <t>Hoets hem elc dats mijn raet / Dat ic dit werc ierst ane ginc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Daer men te hemelrike comt mede / Dat was Christus in waerre dinc</t>
+          <t>Al sijn leven hoe dat gaet / Ende en weet sijns ghenen raet</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>en zijn heilig minne mede / en na dit leven hemelrijk</t>
+          <t>hoe zij hij elk dat zijn mijn raad / dat ik dit werk eerst eindigen gaan</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>daar men te hemelrijk komen mede / dat zijn NOU-P in waar ding</t>
+          <t>al zijn leven hoe dat gaan / en ne weten zijne gene raad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3632,31 +3632,31 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
-        <v>0.5872721904783518</v>
+        <v>0.5827725400717838</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>218</v>
+        <v>156</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dat hi ons geve sine vrede / Ende sine helige minne mede</t>
+          <t>Het es te swaer elcken man / Ende oec some ander dinc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ende es altoes eersam mede / Gherne so houdt si in vreden</t>
+          <t>Ende dan van elken dinghen / Die boden doen te livereren</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>dat hij ons geven zijn vrede / en zijn heilig minne mede</t>
+          <t>het zijn te zwaar elk man / en ook som ander ding</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>en zijn altoos eerzaam mede / gaarne zo houden zij in vrede</t>
+          <t>en dan van elk ding / die bode doen te livereren</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3672,31 +3672,31 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
-        <v>0.5875650149784033</v>
+        <v>0.5830764018353508</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>156</v>
+        <v>61</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Het es te swaer elcken man / Ende oec some ander dinc</t>
+          <t>Dant die edele wise clerc / Selve dichte in sijn werc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ende dan van elken dinghen / Die boden doen te livereren</t>
+          <t>Es voer Gode also mare / Alse eens clercs des benic wijs</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>het zijn te zwaar elk man / en ook som ander ding</t>
+          <t>dan het die edel wijs klerk / zelf dichten in zijn werk</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>en dan van elk ding / die bode doen te livereren</t>
+          <t>zijn voor NOU-P alzo maar / als een klerk de benig wijs</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3712,7 +3712,7 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
-        <v>0.5896595309544017</v>
+        <v>0.58479969358296</v>
       </c>
     </row>
     <row r="83">
@@ -3752,31 +3752,31 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>0.590077469030868</v>
+        <v>0.5897933580276268</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hoets hem elc dats mijn raet / Dat ic dit werc ierst ane ginc</t>
+          <t>Ende lant ende stede ende borge te winnen / Daer anders niet inne en leit</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Al sijn leven hoe dat gaet / Ende en weet sijns ghenen raet</t>
+          <t>Beyde Roelande ende Oliviere / Ende dat heylighe lant winnen</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>hoe zij hij elk dat zijn mijn raad / dat ik dit werk eerst eindigen gaan</t>
+          <t>en land en stede en borg te winnen / daar anders niet in ne liggen</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>al zijn leven hoe dat gaan / en ne weten zijne gene raad</t>
+          <t>beide NOU-P en NOU-P / en dat heilig land winnen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3792,31 +3792,31 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>0.5942680471276677</v>
+        <v>0.5905203116571258</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>82</v>
+        <v>203</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dat en dedic omme gene dinc / Anders dan dat ic niet en woude</t>
+          <t>Die desen bouc selen scauwen / Dat sij Gode bidden vor mi</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dat en es anders niet te verstane / Dan in despijt dat segghic u</t>
+          <t>Desen boec sal ic hem senden / Ende hi sal heten Ians Teesteye</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>dat ne doen ik om geen ding / anders dan dat ik niet ne willen</t>
+          <t>die deze boek zullen schouwen / dat zij NOU-P bidden voor ik</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>dat ne zijn anders niet te verstaan / dan in despijt dat zeggen ik u</t>
+          <t>deze boek zullen ik hij zenden / en hij zullen heten NOU-P teestei</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3832,31 +3832,31 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>0.5953062925471458</v>
+        <v>0.5912394032355115</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ende lant ende stede ende borge te winnen / Daer anders niet inne en leit</t>
+          <t>Hadde bekeert te sinen ghebode / Dit was naer Noe VIIIc iaer</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Beyde Roelande ende Oliviere / Ende dat heylighe lant winnen</t>
+          <t>Dat ghelove al sine iaer / Ende leerde die salighe ghebode</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>en land en stede en borg te winnen / daar anders niet in ne liggen</t>
+          <t>hebben bekeren te zijn gebod / dit zijn naar NOU-P achttiende jaar</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>beide NOU-P en NOU-P / en dat heilig land winnen</t>
+          <t>dat geloof al zijn jaar / en leren die zalig gebod</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3872,31 +3872,31 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
-        <v>0.5955291392103376</v>
+        <v>0.5916802087141433</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Want die leringe die es goet / Beide ter zielen ende ten live</t>
+          <t>Wanen soe quam u dat / Dat God ende ghi allene</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Beyde ziele ende lijf / Ende ghedoghet menech coude</t>
+          <t>Vander broesheyt der wive / Ende wanen dat ic allene</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>want die lering die zijn goed / beide ter ziel en ten lijf</t>
+          <t>waan zo komen u dat / dat NOU-P en gij alleen</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>beide ziel en lijf / en gedogen menig koude</t>
+          <t>van de broesheid de wijf / en wanen dat ik alleen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3912,31 +3912,31 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
-        <v>0.5988575148134578</v>
+        <v>0.5945437607519588</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Soe quam my een boec ter hant / Daer ic in bescreven vant</t>
+          <t>Daer sy clene profijt inne leren / Alsoe sijn geesten vanden heren</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dat si wel te verstane gheven / In haren boeken die si hebben bescreven</t>
+          <t>Die daer te voren was herde cleyne / Hier ane so machmen leren</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>zo komen ik een boek ter hand / daar ik in beschrijven vinden</t>
+          <t>daar zij klein profijt in leren / alzo zijn geest van de heer</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>dat zij wel te verstaan geven / in haar boek die zij hebben beschrijven</t>
+          <t>die daar te voren zijn hard klein / hier aan zo mogen men leren</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3952,31 +3952,31 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
-        <v>0.6009715067631971</v>
+        <v>0.5967796547701552</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wanen soe quam u dat / Dat God ende ghi allene</t>
+          <t>Dat ic dit werc ierst ane ginc / Dat en dedic omme gene dinc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Vander broesheyt der wive / Ende wanen dat ic allene</t>
+          <t>So souden si in hare dinc / Den wech gaen dien Cristus ghinc</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>waan zo komen u dat / dat NOU-P en gij alleen</t>
+          <t>dat ik dit werk eerst eindigen gaan / dat ne doen ik om geen ding</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>van de broesheid de wijf / en wanen dat ik alleen</t>
+          <t>zo zullen zij in haar ding / de weg gaan dat NOU-P gaan</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3992,31 +3992,31 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
-        <v>0.6022684183261322</v>
+        <v>0.5971897756132347</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Met dichtene minen sin / Daer sonder ic nemmeer en ben</t>
+          <t>Want die leringe die es goet / Beide ter zielen ende ten live</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mijn sen en mach niet ledech wesen / In moet scriven dichten of lesen</t>
+          <t>Beyde ziele ende lijf / Ende ghedoghet menech coude</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>met dichten mijn zin / daar zonder ik nimmer ne zijn</t>
+          <t>want die lering die zijn goed / beide ter ziel en ten lijf</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>mijn zin ne mogen niet ledig wezen / u moeten schrijven dichten of lezen</t>
+          <t>beide ziel en lijf / en gedogen menig koude</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4032,31 +4032,31 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
-        <v>0.6035212578594364</v>
+        <v>0.5978186262090706</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>11</v>
+        <v>170</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dan vechten ende vrouwen te minnen / Ende lant ende stede ende borge te winnen</t>
+          <t>Des Soens daer ghi moeder af sijt / Ende die selve Sone es God</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Beyde Roelande ende Oliviere / Ende dat heylighe lant winnen</t>
+          <t>Haren sone Constantine / Ende alle die kindre sine</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>dan vechten en vrouw te minnen / en land en stede en borg te winnen</t>
+          <t>de zoens daar gij moeder af zijn / en die zelf zoon zijn NOU-P</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>beide NOU-P en NOU-P / en dat heilig land winnen</t>
+          <t>haar zoon NOU-P / en al die kind zijn</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4072,31 +4072,31 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
-        <v>0.6041524587920051</v>
+        <v>0.5986161952265834</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>158</v>
+        <v>11</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Die my int herte niet en ginc / Hebbic al gelaten uut</t>
+          <t>Dan vechten ende vrouwen te minnen / Ende lant ende stede ende borge te winnen</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ic ontsie mi des sonder waen / Dat over hem noch wt sal gaen</t>
+          <t>Beyde Roelande ende Oliviere / Ende dat heylighe lant winnen</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>die ik in het hart niet ne gaan / hebben ik al laten uiten</t>
+          <t>dan vechten en vrouw te minnen / en land en stede en borg te winnen</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ik ontzien ik des zonder waan / dat over hij nog uiten zullen gaan</t>
+          <t>beide NOU-P en NOU-P / en dat heilig land winnen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4112,31 +4112,31 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
-        <v>0.6047467588063649</v>
+        <v>0.5995481896032404</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hadde bekeert te sinen ghebode / Dit was naer Noe VIIIc iaer</t>
+          <t>Ende minen zin also verclaerde / Dat ic dit werc met minen arbeide</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dat ghelove al sine iaer / Ende leerde die salighe ghebode</t>
+          <t>Die dinc ende bat verclaren / Dan si vore verclaert waren</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>hebben bekeren te zijn gebod / dit zijn naar NOU-P achttiende jaar</t>
+          <t>en mijn zin alzo verklaren / dat ik dit werk met mijn arbeid</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>dat geloof al zijn jaar / en leren die zalig gebod</t>
+          <t>die ding en bet verklaren / dan zij voor verklaren zijn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4152,31 +4152,31 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
-        <v>0.6047796774011511</v>
+        <v>0.6004701098367202</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Daer sy clene profijt inne leren / Alsoe sijn geesten vanden heren</t>
+          <t>Die my int herte niet en ginc / Hebbic al gelaten uut</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Die daer te voren was herde cleyne / Hier ane so machmen leren</t>
+          <t>Ic ontsie mi des sonder waen / Dat over hem noch wt sal gaen</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>daar zij klein profijt in leren / alzo zijn geest van de heer</t>
+          <t>die ik in het hart niet ne gaan / hebben ik al laten uiten</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>die daar te voren zijn hard klein / hier aan zo mogen men leren</t>
+          <t>ik ontzien ik des zonder waan / dat over hij nog uiten zullen gaan</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4192,31 +4192,31 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>0.6053140574752527</v>
+        <v>0.6011087900728878</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dus quamen in hare scone / Beide die heilege Geest ende die Sone</t>
+          <t>Dat en dedic omme gene dinc / Anders dan dat ic niet en woude</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Des onne ons ende gheve sijn volleest / Die Vader die Sone die Heilighe Gheest</t>
+          <t>Dat en es anders niet te verstane / Dan in despijt dat segghic u</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>dus komen in haar scone / beide die heilig geest en die zoon</t>
+          <t>dat ne doen ik om geen ding / anders dan dat ik niet ne willen</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>de on ons en geven zijn volleest / die vader die zoon die heilig geest</t>
+          <t>dat ne zijn anders niet te verstaan / dan in despijt dat zeggen ik u</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4232,31 +4232,31 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
-        <v>0.6076678383862445</v>
+        <v>0.6027190004620695</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>195</v>
+        <v>115</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ende minen zin also verclaerde / Dat ic dit werc met minen arbeide</t>
+          <t>Daer de warelt zal nemen fijn / Ende de welke behouden zal sijn</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Die dinc ende bat verclaren / Dan si vore verclaert waren</t>
+          <t>Ende metten heylighen inglen fijn / Daer wi allen toe ghenoedt sijn</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>en mijn zin alzo verklaren / dat ik dit werk met mijn arbeid</t>
+          <t>daar de wereld zullen nemen fijn / en de welk behouden zullen zijn</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>die ding en bet verklaren / dan zij voor verklaren zijn</t>
+          <t>en met de heilig engel fijn / daar wij al toe noeden zijn</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4272,31 +4272,31 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
-        <v>0.6076786181686621</v>
+        <v>0.6028736729341191</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Des Soens daer ghi moeder af sijt / Ende die selve Sone es God</t>
+          <t>Soe quam my een boec ter hant / Daer ic in bescreven vant</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Haren sone Constantine / Ende alle die kindre sine</t>
+          <t>Dat si wel te verstane gheven / In haren boeken die si hebben bescreven</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>de zoens daar gij moeder af zijn / en die zelf zoon zijn NOU-P</t>
+          <t>zo komen ik een boek ter hand / daar ik in beschrijven vinden</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>haar zoon NOU-P / en al die kind zijn</t>
+          <t>dat zij wel te verstaan geven / in haar boek die zij hebben beschrijven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4312,31 +4312,31 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
-        <v>0.6079794461650765</v>
+        <v>0.6037628192968527</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Die boec daer icse ute trac / Es geheten die wise Sidrac</t>
+          <t>Dat hy inden Walsce lach / Omme dat ic van dier edelre leren</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Also alse die wise segghen / Die scrifturen in boeken legghen</t>
+          <t>Om der goeder liede leren / So dat God wilde toghen</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>die boek daar ik zij uit trekken / zijn heten die wijze NOU-P</t>
+          <t>dat hij in de wals lachen / om dat ik van die edel leer</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>alzo als die wijze zeggen / die schriftuur in boek leggen</t>
+          <t>om de goed lieden leer / zo dat NOU-P willen togen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4352,31 +4352,31 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
-        <v>0.6088492990612909</v>
+        <v>0.6046395403228859</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dat hy inden Walsce lach / Omme dat ic van dier edelre leren</t>
+          <t>Die nemmermeer no wijf no man / Daer na weder verhalen en can</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Om der goeder liede leren / So dat God wilde toghen</t>
+          <t>Ende datmen nieman en heet vroet man / Die loesheyt noch scalcheyt niet en can</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>dat hij in de wals lachen / om dat ik van die edel leer</t>
+          <t>die nimmermeer noch wijf noch man / daar na weder verhalen ne kunnen</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>om de goed lieden leer / zo dat NOU-P willen togen</t>
+          <t>en dat men niemand ne heten vroed man / die loosheid noch schalkheid niet ne kunnen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4392,31 +4392,31 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
-        <v>0.6094857492132436</v>
+        <v>0.6054430726070494</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Die nemmermeer no wijf no man / Daer na weder verhalen en can</t>
+          <t>Met dichtene minen sin / Daer sonder ic nemmeer en ben</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Daer om en sal nemmermere / Man sijn wijf prisen te sere</t>
+          <t>Mijn sen en mach niet ledech wesen / In moet scriven dichten of lesen</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>die nimmermeer noch wijf noch man / daar na weder verhalen ne kunnen</t>
+          <t>met dichten mijn zin / daar zonder ik nimmer ne zijn</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>daar om ne zullen nimmermeer / man zijn wijf prijzen te zeer</t>
+          <t>mijn zin ne mogen niet ledig wezen / u moeten schrijven dichten of lezen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4432,31 +4432,31 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
-        <v>0.6098040030163749</v>
+        <v>0.606427999395055</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dat ic dit werc ierst ane ginc / Dat en dedic omme gene dinc</t>
+          <t>Van ere tale in een ander tale / Die sal den text leggen dan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>So souden si in hare dinc / Den wech gaen dien Cristus ghinc</t>
+          <t>Gheven ende can oec wel sijn tale / Ende wint den andren al sijn goet</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>dat ik dit werk eerst eindigen gaan / dat ne doen ik om geen ding</t>
+          <t>van een taal in een ander taal / die zullen de tekst leggen dan</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>zo zullen zij in haar ding / de weg gaan dat NOU-P gaan</t>
+          <t>geven en kunnen ook wel zijn taal / en winnen de ander al zijn goed</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4472,7 +4472,7 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
-        <v>0.6105434590221792</v>
+        <v>0.6075343353081217</v>
       </c>
     </row>
     <row r="102">
@@ -4512,31 +4512,31 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
-        <v>0.6117428620313352</v>
+        <v>0.6079551439429756</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ende vele meer dan ontsint / Die dese vrouwe niet en mint</t>
+          <t>Ende gheworpen in die pine / Hoe hem in die helle staet te sine</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Meer dan hen hadde ghemint / Ia die kindre van Ysrael</t>
+          <t>In sire bitterre pinen / Hoe die sonne liet haer schinen</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>en veel meer dan ontzinnen / die deze vrouwe niet ne minnen</t>
+          <t>en werpen in die pijn / hoe hij in die hel staan te zijn</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>meer dan zij hebben minnen / ja die kind van NOU-P</t>
+          <t>in zijn bitter pijn / hoe die zon laten zij schijnen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4552,31 +4552,31 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
-        <v>0.6132433416475755</v>
+        <v>0.608034872232154</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ende gheworpen in die pine / Hoe hem in die helle staet te sine</t>
+          <t>Die Sydrac leerde die vroede / Eenen onghelovighen coninc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>In sire bitterre pinen / Hoe die sonne liet haer schinen</t>
+          <t>Dies menech niet en wilt wesen vroet / Ende dan voert sal ic u leren</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>en werpen in die pijn / hoe hij in die hel staan te zijn</t>
+          <t>die sidrac leren die vroed / een ongelovig koning</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>in zijn bitter pijn / hoe die zon laten zij schijnen</t>
+          <t>dies menig niet ne willen wezen vroed / en dan voort zullen ik u leren</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4592,31 +4592,31 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="n">
-        <v>0.6136004546017959</v>
+        <v>0.6092873278315988</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Daer de warelt zal nemen fijn / Ende de welke behouden zal sijn</t>
+          <t>Dus quamen in hare scone / Beide die heilege Geest ende die Sone</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ende metten heylighen inglen fijn / Daer wi allen toe ghenoedt sijn</t>
+          <t>Des onne ons ende gheve sijn volleest / Die Vader die Sone die Heilighe Gheest</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>daar de wereld zullen nemen fijn / en de welk behouden zullen zijn</t>
+          <t>dus komen in haar scone / beide die heilig geest en die zoon</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>en met de heilig engel fijn / daar wij al toe noeden zijn</t>
+          <t>de on ons en geven zijn volleest / die vader die zoon die heilig geest</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4632,31 +4632,31 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
-        <v>0.6150563308974564</v>
+        <v>0.6104458556141086</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Van ere tale in een ander tale / Die sal den text leggen dan</t>
+          <t>Ende vele meer dan ontsint / Die dese vrouwe niet en mint</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Gheven ende can oec wel sijn tale / Ende wint den andren al sijn goet</t>
+          <t>Meer dan hen hadde ghemint / Ia die kindre van Ysrael</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>van een taal in een ander taal / die zullen de tekst leggen dan</t>
+          <t>en veel meer dan ontzinnen / die deze vrouwe niet ne minnen</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>geven en kunnen ook wel zijn taal / en winnen de ander al zijn goed</t>
+          <t>meer dan zij hebben minnen / ja die kind van NOU-P</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4672,31 +4672,31 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
-        <v>0.6154822479499316</v>
+        <v>0.6109412728804482</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Die Sydrac leerde die vroede / Eenen onghelovighen coninc</t>
+          <t>Ende hebbe versleten nochtan / Met dichtene minen sin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ende te lerene gheven den vroeden / Ende als si dan wassen in die joeght</t>
+          <t>Nochtan dunct in sinen sinne / Hem die verliest dat goet</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>die sidrac leren die vroed / een ongelovig koning</t>
+          <t>en hebben verslijten nochtan / met dichten mijn zin</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>en te leren geven de vroed / en als zij dan wassen in die jong</t>
+          <t>nochtan dunken in zijn zin / hij die verliezen dat goed</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4712,31 +4712,31 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>0.6157099457137709</v>
+        <v>0.6113569028670315</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Omme dat wy in dit leven / Dat overlijt soe cortelike</t>
+          <t>Dat ic dit boec woude maken / Uten Walsche in Dietsche spraken</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hier in dit arme leven / Aldus so nemen inde</t>
+          <t>Ontfermhertich ende ghenadech / Waerwoerdech in hare spraken</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>om dat wij in dit leven / dat overlijd zo kortelijk</t>
+          <t>dat ik dit boek willen maken / uit dat Waals in Diets spraak</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>hier in dit arm leven / aldus zo nemen in de</t>
+          <t>ontfermhartig en genadig / waarwoordig in haar spraak</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4752,31 +4752,31 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>0.6179423057924074</v>
+        <v>0.6124964926917353</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Want sy den tyt verliesen / Die nemmermeer no wijf no man</t>
+          <t>Omme dat wy in dit leven / Dat overlijt soe cortelike</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ende niet en spaerden des mans no wijf / Ofte dat si meer int lant en quamen</t>
+          <t>Hier in dit arme leven / Aldus so nemen inde</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>want zij de tijd verliezen / die nimmermeer noch wijf noch man</t>
+          <t>om dat wij in dit leven / dat overlijd zo kortelijk</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>en niet ne sparen de man noch wijf / ofte dat zij meer in het land ne komen</t>
+          <t>hier in dit arm leven / aldus zo nemen in de</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4792,31 +4792,31 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>0.6181290882646411</v>
+        <v>0.6156563279040568</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daer sonder ic nemmeer en ben / In dichte niet dat weet wale</t>
+          <t>Die sal den text leggen dan / Soe hy alre gelijcxt can</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Die asaghen ende tureluren / Dichten vander avonturen</t>
+          <t>Willict u vertrecken dan / So ict alder best can</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>daar zonder ik nimmer ne zijn / in dicht niet dat weten wel</t>
+          <t>die zullen de tekst leggen dan / zo hij al gelijk kunnen</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>die asage en tureluur / dicht van de avontuur</t>
+          <t>willigen u vertrekken dan / zo ik het al goed kunnen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4832,31 +4832,31 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>0.6186128435195848</v>
+        <v>0.6161455946484216</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dat ic dit boec woude maken / Uten Walsche in Dietsche spraken</t>
+          <t>Die boec daer icse ute trac / Es geheten die wise Sidrac</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ontfermhertich ende ghenadech / Waerwoerdech in hare spraken</t>
+          <t>Also alse die wise segghen / Die scrifturen in boeken legghen</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>dat ik dit boek willen maken / uit dat Waals in Diets spraak</t>
+          <t>die boek daar ik zij uit trekken / zijn heten die wijze NOU-P</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ontfermhartig en genadig / waarwoordig in haar spraak</t>
+          <t>alzo als die wijze zeggen / die schriftuur in boek leggen</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4872,31 +4872,31 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>0.619225228010098</v>
+        <v>0.6165761034238011</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ende hebbe versleten nochtan / Met dichtene minen sin</t>
+          <t>Waer of wi ons zouden hoeden / Die Sydrac leerde die vroede</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nochtan dunct in sinen sinne / Hem die verliest dat goet</t>
+          <t>Dies menech niet en wilt wesen vroet / Ende dan voert sal ic u leren</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>en hebben verslijten nochtan / met dichten mijn zin</t>
+          <t>waar af wij ons zullen hoeden / die sidrac leren die vroed</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>nochtan dunken in zijn zin / hij die verliezen dat goed</t>
+          <t>dies menig niet ne willen wezen vroed / en dan voort zullen ik u leren</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4912,31 +4912,31 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>0.6201682151962914</v>
+        <v>0.616578272264404</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Dat sy selen daer omme bedi / Vriendelike bidden voir my</t>
+          <t>Want sy den tyt verliesen / Die nemmermeer no wijf no man</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bedi si moeten leven / Van datmen hem sal gheven</t>
+          <t>Ende niet en spaerden des mans no wijf / Ofte dat si meer int lant en quamen</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>dat zij zullen daar om bedie / vriendelijk bidden voor ik</t>
+          <t>want zij de tijd verliezen / die nimmermeer noch wijf noch man</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>bedie zij moeten leven / van dat men hij zullen geven</t>
+          <t>en niet ne sparen de man noch wijf / ofte dat zij meer in het land ne komen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4952,31 +4952,31 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>0.6201912477654173</v>
+        <v>0.6183532080993157</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Waer of wi ons zouden hoeden / Die Sydrac leerde die vroede</t>
+          <t>Uten Walsche in Dietsche spraken / Sonder rime alsoe ic sach</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dies menech niet en wilt wesen vroet / Ende dan voert sal ic u leren</t>
+          <t>Ontfermhertich ende ghenadech / Waerwoerdech in hare spraken</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>waar af wij ons zullen hoeden / die sidrac leren die vroed</t>
+          <t>uit dat Waals in Diets spraak / zonder rijm alzo ik zien</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>dies menig niet ne willen wezen vroed / en dan voort zullen ik u leren</t>
+          <t>ontfermhartig en genadig / waarwoordig in haar spraak</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4992,31 +4992,31 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>0.6226227916278722</v>
+        <v>0.6185962334935199</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Metten inglen daer boven / Ende oec die werden verscroven</t>
+          <t>Hy es Vader gebenedijt / Des Soens daer ghi moeder af sijt</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Es hier boven met Onsen Here / Ende metten heylighen inglen fijn</t>
+          <t>Si es ons ghereet in alre tijt / Des moet si sijn ghebenedijt</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>met de engel daar boven / en ook die worden verschruiven</t>
+          <t>hij zijn vader benedijen / de zoens daar gij moeder af zijn</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>zijn hier boven met ons heer / en met de heilig engel fijn</t>
+          <t>zij zijn ons gereed in al tijd / des moeten zij zijn benedijen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5032,7 +5032,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>0.6227740628908043</v>
+        <v>0.6190091098665629</v>
       </c>
     </row>
     <row r="116">
@@ -5072,31 +5072,31 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="n">
-        <v>0.6250173822115006</v>
+        <v>0.6196981051918093</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Uten Walsche in Dietsche spraken / Sonder rime alsoe ic sach</t>
+          <t>Dat sy selen daer omme bedi / Vriendelike bidden voir my</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ontfermhertich ende ghenadech / Waerwoerdech in hare spraken</t>
+          <t>Bedi si moeten leven / Van datmen hem sal gheven</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>uit dat Waals in Diets spraak / zonder rijm alzo ik zien</t>
+          <t>dat zij zullen daar om bedie / vriendelijk bidden voor ik</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ontfermhartig en genadig / waarwoordig in haar spraak</t>
+          <t>bedie zij moeten leven / van dat men hij zullen geven</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5112,7 +5112,7 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
-        <v>0.6257599415458306</v>
+        <v>0.6205142514693658</v>
       </c>
     </row>
     <row r="118">
@@ -5152,31 +5152,31 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
-        <v>0.6261604579663367</v>
+        <v>0.6217592892158489</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Die sal den text leggen dan / Soe hy alre gelijcxt can</t>
+          <t>Den Dietscen lieden verholen wesen / Die geen Walsch en connen lesen</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Willict u vertrecken dan / So ict alder best can</t>
+          <t>Wouter sal ic die waerheyt lesen / Heren souden scemel wesen</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>die zullen de tekst leggen dan / zo hij al gelijk kunnen</t>
+          <t>de Diets lieden verhelen wezen / die geen Waals ne kunnen lezen</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>willigen u vertrekken dan / zo ik het al goed kunnen</t>
+          <t>wouter zullen ik die waarheid lezen / heer zullen schemel wezen</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5192,7 +5192,7 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>0.6285363676014585</v>
+        <v>0.6229239002398512</v>
       </c>
     </row>
     <row r="120">
@@ -5232,31 +5232,31 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>0.6293045633002764</v>
+        <v>0.6243524678863936</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hy es Vader gebenedijt / Des Soens daer ghi moeder af sijt</t>
+          <t>Daer sonder ic nemmeer en ben / In dichte niet dat weet wale</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Si es ons ghereet in alre tijt / Des moet si sijn ghebenedijt</t>
+          <t>Die asaghen ende tureluren / Dichten vander avonturen</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>hij zijn vader benedijen / de zoens daar gij moeder af zijn</t>
+          <t>daar zonder ik nimmer ne zijn / in dicht niet dat weten wel</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>zij zijn ons gereed in al tijd / des moeten zij zijn benedijen</t>
+          <t>die asage en tureluur / dicht van de avontuur</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5272,31 +5272,31 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
-        <v>0.6297747761071043</v>
+        <v>0.6246408440139255</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Na enen clerc wijs ende fijn / Was philosophe ende astronomijn</t>
+          <t>Daer men ginder af ontfaet / Hondertfout van lone</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ende wiese heeft int herte sijn / Dats een recht dorpre fijn</t>
+          <t>Dat hi broet bidden gaet / Ende wilt daer in verdienen lone</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>na een klerk wijs en fijn / zijn filosoof en astronomijn</t>
+          <t>daar men ginder af ontvangen / honderdfout van loon</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>en wijs hebben in het hart zijn / dat zijn een recht dorper fijn</t>
+          <t>dat hij brood bidden gaan / en willen daar in verdienen loon</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5312,31 +5312,31 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
-        <v>0.6309216266625106</v>
+        <v>0.6269078429496742</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dat hi mi dan al mine zonden / Verre van mi wille werpen</t>
+          <t>Want ict niewer omme dede / Dan omme gemene zalichede</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ic rade wel elken man / Dat hi hem huede van sonden</t>
+          <t>Oec eest grote salichede / Datmen den tijt onledech make</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>dat hij ik dan al mijn zonde / ver van ik willen werpen</t>
+          <t>want ik het niewer om doen / dan om gemeen zaligheid</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ik raden wel elk man / dat hij hij houden van zonde</t>
+          <t>ook zijn het groot zaligheid / dat men de tijd onledige maken</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5352,31 +5352,31 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
-        <v>0.6348694829905642</v>
+        <v>0.6270439055930315</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Daer men ginder af ontfaet / Hondertfout van lone</t>
+          <t>Na enen clerc wijs ende fijn / Was philosophe ende astronomijn</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dat hi broet bidden gaet / Ende wilt daer in verdienen lone</t>
+          <t>Ende wiese heeft int herte sijn / Dats een recht dorpre fijn</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>daar men ginder af ontvangen / honderdfout van loon</t>
+          <t>na een klerk wijs en fijn / zijn filosoof en astronomijn</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>dat hij brood bidden gaan / en willen daar in verdienen loon</t>
+          <t>en wijs hebben in het hart zijn / dat zijn een recht dorper fijn</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5392,31 +5392,31 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
-        <v>0.6353316469846395</v>
+        <v>0.6273866997533326</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Vele duechden ende wijsheden / Ende leringe van goeden seden</t>
+          <t>Metten inglen daer boven / Ende oec die werden verscroven</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Haers abds volmaecte seden / Van dogheden ende van oetmoedecheden</t>
+          <t>Es hier boven met Onsen Here / Ende metten heylighen inglen fijn</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>veel deugd en wijsheid / en lering van goed zede</t>
+          <t>met de engel daar boven / en ook die worden verschruiven</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>haar abt volmaakt zede / van deugd en van ootmoedigheid</t>
+          <t>zijn hier boven met ons heer / en met de heilig engel fijn</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5432,31 +5432,31 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
-        <v>0.6359551922398596</v>
+        <v>0.6290493632038456</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Want ict niewer omme dede / Dan omme gemene zalichede</t>
+          <t>Ghelooft zi God van hemelrike / In sine glorie ewelike</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oec eest grote salichede / Datmen den tijt onledech make</t>
+          <t>God gheve hem sijn hemelrike / Nu hebdi verstaen die nuthede</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>want ik het niewer om doen / dan om gemeen zaligheid</t>
+          <t>loven zij NOU-P van hemelrijk / in zijn glorie eeuwelijk</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ook zijn het groot zaligheid / dat men de tijd onledige maken</t>
+          <t>NOU-P geven hij zijn hemelrijk / nu hebben gij verstaan die nutheid</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5472,31 +5472,31 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
-        <v>0.6364946590003306</v>
+        <v>0.630163579112948</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Den Dietscen lieden verholen wesen / Die geen Walsch en connen lesen</t>
+          <t>Dat ic dit werc met minen arbeide / Uten Walsce in Dietsce leide</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wouter sal ic die waerheyt lesen / Heren souden scemel wesen</t>
+          <t>Daer dat volc met omme ghinc / Want groet waer mi die arbeyt</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>de Diets lieden verhelen wezen / die geen Waals ne kunnen lezen</t>
+          <t>dat ik dit werk met mijn arbeid / uit dat wals in Diets leed</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>wouter zullen ik die waarheid lezen / heer zullen schemel wezen</t>
+          <t>daar dat volk met om gaan / want groot zijn ik die arbeid</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5512,31 +5512,31 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
-        <v>0.6365041218904806</v>
+        <v>0.6303095223930058</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hoe hem in die helle staet te sine / Van vagheviere ende van paradise mede</t>
+          <t>Dat hi mi dan al mine zonden / Verre van mi wille werpen</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Yerst maecte inden paradise / Dits doerdene daert al aen steet</t>
+          <t>Ic rade wel elken man / Dat hi hem huede van sonden</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>hoe hij in die hel staan te zijn / van vagevuur en van paradijs mede</t>
+          <t>dat hij ik dan al mijn zonde / ver van ik willen werpen</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>eerst maken in de paradijs / dit zijn doorde daar het al aan staan</t>
+          <t>ik raden wel elk man / dat hij hij houden van zonde</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5552,31 +5552,31 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="n">
-        <v>0.6373262929819314</v>
+        <v>0.6308036652583591</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>196</v>
+        <v>103</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dat ic dit werc met minen arbeide / Uten Walsce in Dietsce leide</t>
+          <t>Van firmamenten ende van planeten / Hoe der inglen coor sijn gheheten</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Daer dat volc met omme ghinc / Want groet waer mi die arbeyt</t>
+          <t>Want si mochtent merken ende weten / Aen delemente ende aen de planeten</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>dat ik dit werk met mijn arbeid / uit dat wals in Diets leed</t>
+          <t>van firmament en van planeet / hoe de engel koor zijn heten</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>daar dat volk met om gaan / want groot zijn ik die arbeid</t>
+          <t>want zij mogen het merken en weten / aan delement en aan de planeet</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5592,31 +5592,31 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="n">
-        <v>0.6375194885056739</v>
+        <v>0.6310511551041667</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ghelooft zi God van hemelrike / In sine glorie ewelike</t>
+          <t>Vele duechden ende wijsheden / Ende leringe van goeden seden</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>God gheve hem sijn hemelrike / Nu hebdi verstaen die nuthede</t>
+          <t>Haers abds volmaecte seden / Van dogheden ende van oetmoedecheden</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>loven zij NOU-P van hemelrijk / in zijn glorie eeuwelijk</t>
+          <t>veel deugd en wijsheid / en lering van goed zede</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>NOU-P geven hij zijn hemelrijk / nu hebben gij verstaan die nutheid</t>
+          <t>haar abt volmaakt zede / van deugd en van ootmoedigheid</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5632,31 +5632,31 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="n">
-        <v>0.6382400177342027</v>
+        <v>0.6343844807205465</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ende leringe van goeden seden / Ende hoe die mensce soude leven</t>
+          <t>Van vagheviere ende van paradise mede / Ende oerbare leringhe in menigher stede</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>So en was Cristus leven anders niet / Dan exemple ende leringhe mede</t>
+          <t>Ende Cristus vicarise mede / Gheset in sine heylighe stede</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>en lering van goed zede / en hoe die mens zullen leven</t>
+          <t>van vagevuur en van paradijs mede / en oorbaar lering in menig stede</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>zo ne zijn NOU-P leven anders niet / dan exempel en lering mede</t>
+          <t>en NOU-P vicarise mede / zetten in zijn heilig stede</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5672,31 +5672,31 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="n">
-        <v>0.6383163145962311</v>
+        <v>0.6354407472966531</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dien boec ute altemale / Vanden cruden latic uut</t>
+          <t>Hoe hem in die helle staet te sine / Van vagheviere ende van paradise mede</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wat du laets gaen wt dinen monde / Wt dinen nase wt dinen oren</t>
+          <t>Yerst maecte inden paradise / Dits doerdene daert al aen steet</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>dat boek uit altemaal / van de kruid laten ik uit</t>
+          <t>hoe hij in die hel staan te zijn / van vagevuur en van paradijs mede</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>wat du laten gaan uit dijn mond / uit dijn neus uit dijn oor</t>
+          <t>eerst maken in de paradijs / dit zijn doorde daar het al aan staan</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5712,31 +5712,31 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="n">
-        <v>0.6398103330321234</v>
+        <v>0.6355075788748352</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Van firmamenten ende van planeten / Hoe der inglen coor sijn gheheten</t>
+          <t>Soe hy alre gelijcxt can / Dit sal van rechte sijn sine sede</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Want si mochtent merken ende weten / Aen delemente ende aen de planeten</t>
+          <t>Dit duncken mi al salighe seden / Tfolc en was nie so wel beset</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>van firmament en van planeet / hoe de engel koor zijn heten</t>
+          <t>zo hij al gelijk kunnen / dit zullen van rechte zijn zijn zede</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>want zij mogen het merken en weten / aan delement en aan de planeet</t>
+          <t>dit dunken ik al zalig zede / dat volk ne zijn nie zo wel bezetten</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5752,31 +5752,31 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="n">
-        <v>0.6406244335628812</v>
+        <v>0.638265380054558</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Omme dat ic die pine bestoet / Want die leringe die es goet</t>
+          <t>Daerbeit zal mi wesen zwaer / Want ic oud was vichtich iaer</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Daer om ontseyde die herte sine / Beide die ere ende oec die pine</t>
+          <t>Die meer was dan vjm iaer / Des menschen viant herde swaer</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>om dat ik die pijn bestaan / want die lering die zijn goed</t>
+          <t>daarbeid zullen ik wezen zwaar / want ik oud zijn vijftig jaar</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>daar om ontzeggen die hart zijn / beide die eer en ook die pijn</t>
+          <t>die meer zijn dan vijf jaar / de mens vijand hard zwaar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5792,31 +5792,31 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="n">
-        <v>0.6417252389125834</v>
+        <v>0.638460507373677</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Soe hy alre gelijcxt can / Dit sal van rechte sijn sine sede</t>
+          <t>Daer ic in bescreven vant / Vele duechden ende wijsheden</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dit duncken mi al salighe seden / Tfolc en was nie so wel beset</t>
+          <t>Ende dat onthoudt al sine wijshede / Staende aldus in enen stede</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>zo hij al gelijk kunnen / dit zullen van rechte zijn zijn zede</t>
+          <t>daar ik in beschrijven vinden / veel deugd en wijsheid</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>dit dunken ik al zalig zede / dat volk ne zijn nie zo wel bezetten</t>
+          <t>en dat onthouden al zijn wijsheid / staan aldus in een stede</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5832,7 +5832,7 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
-        <v>0.6419292556637592</v>
+        <v>0.6392863079716681</v>
       </c>
     </row>
     <row r="136">
@@ -5872,7 +5872,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
-        <v>0.643364680843129</v>
+        <v>0.6398432042378046</v>
       </c>
     </row>
     <row r="137">
@@ -5912,7 +5912,7 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="n">
-        <v>0.6450696859643235</v>
+        <v>0.6399232224952447</v>
       </c>
     </row>
     <row r="138">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hemelrijx dan du bes / Die best leeft best es</t>
+          <t>Hi es dat overste goet / Daert al bi steet ende oyt stoet</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>hemelrijks dan du zijn / die goed leven goed zijn</t>
+          <t>hij zijn dat overst goed / daar het al bij staan en ooit staan</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5952,31 +5952,31 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
-        <v>0.6465419611858059</v>
+        <v>0.6417500261525639</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Selve dichte in sijn werc / Want rime alsoe wijt vinden</t>
+          <t>Dien boec ute altemale / Vanden cruden latic uut</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dichte ende ict hem soude senden / Dat hi daer yet mochte venden</t>
+          <t>Wat du laets gaen wt dinen monde / Wt dinen nase wt dinen oren</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>zelf dichten in zijn werk / want rijm alzo wij het vinden</t>
+          <t>dat boek uit altemaal / van de kruid laten ik uit</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>dichten en ik het hij zullen zenden / dat hij daar iet mogen vinden</t>
+          <t>wat du laten gaan uit dijn mond / uit dijn neus uit dijn oor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5992,31 +5992,31 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="n">
-        <v>0.6467547222460971</v>
+        <v>0.6420954458016409</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Want vele beter es wijshede / Danne enighe erdsche rijchede</t>
+          <t>Omme dat ic die pine bestoet / Want die leringe die es goet</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Si quame vander rijcheyt toe / Wouter rijcheyt no gheborte mede</t>
+          <t>Daer om ontseyde die herte sine / Beide die ere ende oec die pine</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>want veel goed zijn wijsheid / dan enig aards rijkheid</t>
+          <t>om dat ik die pijn bestaan / want die lering die zijn goed</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>zij komen van de rijkheid toegespreken / NOU-P rijkheid noch geboorte mede</t>
+          <t>daar om ontzeggen die hart zijn / beide die eer en ook die pijn</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6032,31 +6032,31 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
-        <v>0.6470598923054964</v>
+        <v>0.6423713689004082</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Daer ic in bescreven vant / Vele duechden ende wijsheden</t>
+          <t>Ende leringe van goeden seden / Ende hoe die mensce soude leven</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ende dat onthoudt al sine wijshede / Staende aldus in enen stede</t>
+          <t>So en was Cristus leven anders niet / Dan exemple ende leringhe mede</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>daar ik in beschrijven vinden / veel deugd en wijsheid</t>
+          <t>en lering van goed zede / en hoe die mens zullen leven</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>en dat onthouden al zijn wijsheid / staan aldus in een stede</t>
+          <t>zo ne zijn NOU-P leven anders niet / dan exempel en lering mede</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6072,31 +6072,31 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
-        <v>0.6471008502485617</v>
+        <v>0.6425849154275903</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Hy en deder toe noch af / Anders dant dauctor ute gaf</t>
+          <t>Want vele beter es wijshede / Danne enighe erdsche rijchede</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hi maecter af dan enen sot / Ende hi es diene meest bespot</t>
+          <t>Si quame vander rijcheyt toe / Wouter rijcheyt no gheborte mede</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>hij ne doen er toegespreken nog afhebben hij / anders dan het de autor uiten geven</t>
+          <t>want veel goed zijn wijsheid / dan enig aards rijkheid</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>hij maken er afhebben hij dan een zot / en hij zijn die hij meest bespotten</t>
+          <t>zij komen van de rijkheid toegespreken / NOU-P rijkheid noch geboorte mede</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6112,31 +6112,31 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
-        <v>0.6474887010831654</v>
+        <v>0.645893390968711</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Van vagheviere ende van paradise mede / Ende oerbare leringhe in menigher stede</t>
+          <t>Ende netelen ende distelen plucken gaen / Ende die goede vrucht laten staen</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ende Cristus vicarise mede / Gheset in sine heylighe stede</t>
+          <t>Ende een ure niet stille en steet / Die tijt gheet vaste ende gheet</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>van vagevuur en van paradijs mede / en oorbaar lering in menig stede</t>
+          <t>en netelen en distel plukken gaan / en die goed vrucht laten staan</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>en NOU-P vicarise mede / zetten in zijn heilig stede</t>
+          <t>en een uur niet stillen ne staan / die tijd gaan vast en gaan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6152,31 +6152,31 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
-        <v>0.6485254334585249</v>
+        <v>0.646241374019924</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>200</v>
+        <v>62</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Al der goonre dieze lezen / Ic hope God mijn loon sal wezen</t>
+          <t>Selve dichte in sijn werc / Want rime alsoe wijt vinden</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wouter sal ic die waerheyt lesen / Heren souden scemel wesen</t>
+          <t>Dichte ende ict hem soude senden / Dat hi daer yet mochte venden</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>al de gonder die zij lezen / ik hopen NOU-P mijn loon zullen wijzen</t>
+          <t>zelf dichten in zijn werk / want rijm alzo wij het vinden</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>wouter zullen ik die waarheid lezen / heer zullen schemel wezen</t>
+          <t>dichten en ik het hij zullen zenden / dat hij daar iet mogen vinden</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6192,31 +6192,31 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="n">
-        <v>0.6496127402388996</v>
+        <v>0.6462998530531334</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dicke hebbic die gene bescouden / Die hem ane die boeke houden</t>
+          <t>Al der goonre dieze lezen / Ic hope God mijn loon sal wezen</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ende Moyses boeke hilden si / Ende propheten oec daer bi</t>
+          <t>Wouter sal ic die waerheyt lesen / Heren souden scemel wesen</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>dik hebben ik die geen beschelden / die hij aan die beuk houden</t>
+          <t>al de gonder die zij lezen / ik hopen NOU-P mijn loon zullen wijzen</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>en NOU-P beuk houden zij / en profeten ook daar bij</t>
+          <t>wouter zullen ik die waarheid lezen / heer zullen schemel wezen</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6232,31 +6232,31 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="n">
-        <v>0.6500822473786112</v>
+        <v>0.6463468789809553</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Die God alsoe hadde vercoren / Dat hijt al wiste te voren</t>
+          <t>Daer hi sinen omoet in togede / Dat hi ons geve sine vrede</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>WOuter ic hebbe segghen horen / Dat een coninc hier te voren</t>
+          <t>Ghelijc dat sweert in beyden siden / Ende daer sal hi oec toghen</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>die NOU-P alzo hebben verkiezen / dat hij het al wissen te voren</t>
+          <t>daar hij zijn ootmoed in togen / dat hij ons geven zijn vrede</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>NOU-P ik hebben zeggen horen / dat een koning hier te voren</t>
+          <t>gelijk dat zwaard in beide zijde / en daar zullen hij ook togen</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -6272,31 +6272,31 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="n">
-        <v>0.6513431602428534</v>
+        <v>0.6469623623765723</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Daer hi sinen omoet in togede / Dat hi ons geve sine vrede</t>
+          <t>Die God alsoe hadde vercoren / Dat hijt al wiste te voren</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ghelijc dat sweert in beyden siden / Ende daer sal hi oec toghen</t>
+          <t>WOuter ic hebbe segghen horen / Dat een coninc hier te voren</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>daar hij zijn ootmoed in togen / dat hij ons geven zijn vrede</t>
+          <t>die NOU-P alzo hebben verkiezen / dat hij het al wissen te voren</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>gelijk dat zwaard in beide zijde / en daar zullen hij ook togen</t>
+          <t>NOU-P ik hebben zeggen horen / dat een koning hier te voren</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -6312,31 +6312,31 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="n">
-        <v>0.6516729803791218</v>
+        <v>0.6491582239956551</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Daerbeit zal mi wesen zwaer / Want ic oud was vichtich iaer</t>
+          <t>Maria vol van genaden / Ende staet my in staden</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Die meer was dan vjm iaer / Des menschen viant herde swaer</t>
+          <t>Te comene tot vroeden rade / Beyde in hoven ende in stade</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>daarbeid zullen ik wezen zwaar / want ik oud zijn vijftig jaar</t>
+          <t>NOU-P vol van genade / en staan ik in stade</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>die meer zijn dan vijf jaar / de mens vijand hard zwaar</t>
+          <t>te komen tot vroed raad / beide in hof en in stade</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -6352,31 +6352,31 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="n">
-        <v>0.6519785030284626</v>
+        <v>0.6496999798496252</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ende oec die werden verscroven / Ende gheworpen in die pine</t>
+          <t>Wast dat ic dit translateerde / Doe men Gods iare noteerde</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Daer om ontseyde die herte sine / Beide die ere ende oec die pine</t>
+          <t>So dat tusschen hen bedies / Groet swaer orloghe wies</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>en ook die worden verschruiven / en werpen in die pijn</t>
+          <t>wassen dat ik dit translateren / toen men NOU-P jaar noteren</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>daar om ontzeggen die hart zijn / beide die eer en ook die pijn</t>
+          <t>zo dat tussen zij bedoen / groot zwaar oorlog wassen</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -6392,31 +6392,31 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="n">
-        <v>0.6526156968412238</v>
+        <v>0.6497123359110352</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Die geen Walsch en connen lesen / Noch geen Walsch en verstaen</t>
+          <t>Ende oec die werden verscroven / Ende gheworpen in die pine</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Daer en sal helpen gheen spreken / No gheen dreyghen no gheen smeken</t>
+          <t>Daer om ontseyde die herte sine / Beide die ere ende oec die pine</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>die geen Waals ne kunnen lezen / noch geen Waals ne verstaan</t>
+          <t>en ook die worden verschruiven / en werpen in die pijn</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>daar ne zullen helpen geen spreken / noch geen dreigen noch geen smeken</t>
+          <t>daar om ontzeggen die hart zijn / beide die eer en ook die pijn</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6432,31 +6432,31 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="n">
-        <v>0.6547180173776957</v>
+        <v>0.6500178809057019</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Maria vol van genaden / Ende staet my in staden</t>
+          <t>Hy en deder toe noch af / Anders dant dauctor ute gaf</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Te comene tot vroeden rade / Beyde in hoven ende in stade</t>
+          <t>Hi maecter af dan enen sot / Ende hi es diene meest bespot</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NOU-P vol van genade / en staan ik in stade</t>
+          <t>hij ne doen er toegespreken nog afhebben hij / anders dan het de autor uiten geven</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>te komen tot vroed raad / beide in hof en in stade</t>
+          <t>hij maken er afhebben hij dan een zot / en hij zijn die hij meest bespotten</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6472,31 +6472,31 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="n">
-        <v>0.6552532939234184</v>
+        <v>0.6516127809265483</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ende die hier luttel sayen / Selen ginder luttel mayen</t>
+          <t>Dicke hebbic die gene bescouden / Die hem ane die boeke houden</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Moetic u een luttel ranten / Alse minderbrueder ende jacopine</t>
+          <t>Ende Moyses boeke hilden si / Ende propheten oec daer bi</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>en die hier luttel zaaien / zullen ginder luttel maaien</t>
+          <t>dik hebben ik die geen beschelden / die hij aan die beuk houden</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>moeten ik u een luttel ranten / als minderbreuder en NOU-P</t>
+          <t>en NOU-P beuk houden zij / en profeten ook daar bij</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6512,31 +6512,31 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="n">
-        <v>0.6561732406301692</v>
+        <v>0.6548178452468678</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Wast dat ic dit translateerde / Doe men Gods iare noteerde</t>
+          <t>XIIIc XV ende drie / Bidden wi der maget Marien</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>So dat tusschen hen bedies / Groet swaer orloghe wies</t>
+          <t>Ende een moeten wesen drie / Ic bids u berechtes mie</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>wassen dat ik dit translateren / toen men NOU-P jaar noteren</t>
+          <t>vierentwintig vijftien een drie / bidden wij de maagd NOU-P</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>zo dat tussen zij bedoen / groot zwaar oorlog wassen</t>
+          <t>en een moeten wezen drie / ik bidden dat u berecht ik</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6552,31 +6552,31 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="n">
-        <v>0.6563020748544361</v>
+        <v>0.6582529706701837</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ende netelen ende distelen plucken gaen / Ende die goede vrucht laten staen</t>
+          <t>Die geen Walsch en connen lesen / Noch geen Walsch en verstaen</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ende een ure niet stille en steet / Die tijt gheet vaste ende gheet</t>
+          <t>Daer en sal helpen gheen spreken / No gheen dreyghen no gheen smeken</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>en netelen en distel plukken gaan / en die goed vrucht laten staan</t>
+          <t>die geen Waals ne kunnen lezen / noch geen Waals ne verstaan</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>en een uur niet stillen ne staan / die tijd gaan vast en gaan</t>
+          <t>daar ne zullen helpen geen spreken / noch geen dreigen noch geen smeken</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6592,7 +6592,7 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="n">
-        <v>0.6588946290096606</v>
+        <v>0.6608513504692611</v>
       </c>
     </row>
     <row r="155">
@@ -6632,31 +6632,31 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="n">
-        <v>0.6611899325460884</v>
+        <v>0.6625960564565667</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nochtan half logene es ende mere / Ende anders en hebben engene lere</t>
+          <t>Ende die hier luttel sayen / Selen ginder luttel mayen</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Want al datmer inne vent / Es leren ende bedieden</t>
+          <t>Moetic u een luttel ranten / Alse minderbrueder ende jacopine</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>nochtan half leugen zijn en meer / en anders ne hebben negeen leer</t>
+          <t>en die hier luttel zaaien / zullen ginder luttel maaien</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>want al dat meer ik ne venten / zijn leer en beduiden</t>
+          <t>moeten ik u een luttel ranten / als minderbreuder en NOU-P</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6672,31 +6672,31 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="n">
-        <v>0.6651348736944634</v>
+        <v>0.6627178489098117</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>XIIIc XV ende drie / Bidden wi der maget Marien</t>
+          <t>Dat hi mijns genadich sij / Alst comt te minen laetsten stonden</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ende een moeten wesen drie / Ic bids u berechtes mie</t>
+          <t>Dat hi hem huede van sonden / Ende dat hi peynse tallen stonden</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>vierentwintig vijftien een drie / bidden wij de maagd NOU-P</t>
+          <t>dat hij ik genadig zijn / als het komen te mijn laat stond</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>en een moeten wezen drie / ik bidden dat u berecht ik</t>
+          <t>dat hij hij houden van zonde / en dat hij peinzen te al stond</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6712,7 +6712,7 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="n">
-        <v>0.6668254392564463</v>
+        <v>0.6638471096179779</v>
       </c>
     </row>
     <row r="158">
@@ -6752,31 +6752,31 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="n">
-        <v>0.6670103297955621</v>
+        <v>0.6643181366686841</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Danne ghesteente zelver of gout / Want vele beter es wijshede</t>
+          <t>Nochtan half logene es ende mere / Ende anders en hebben engene lere</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ende wijsheyden dan die here / Maer Wouter sijt seker des</t>
+          <t>Want al datmer inne vent / Es leren ende bedieden</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>dan gesteente zelf of goud / want veel goed zijn wijsheid</t>
+          <t>nochtan half leugen zijn en meer / en anders ne hebben negeen leer</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>en wijsheid dan die heer / maar NOU-P zijn zeker de</t>
+          <t>want al dat meer ik ne venten / zijn leer en beduiden</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6792,31 +6792,31 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="n">
-        <v>0.6677123005850638</v>
+        <v>0.6645121335104358</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Dat hi mijns genadich sij / Alst comt te minen laetsten stonden</t>
+          <t>Dit was naer Noe VIIIc iaer / Ende XLVII daer naer</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dat hi hem huede van sonden / Ende dat hi peynse tallen stonden</t>
+          <t>Voer sine doet noch daer naer / Dat ic u segghe dat es waer</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>dat hij ik genadig zijn / als het komen te mijn laat stond</t>
+          <t>dit zijn naar NOU-P achttiende jaar / en zevenenveertig daar naar</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>dat hij hij houden van zonde / en dat hij peinzen te al stond</t>
+          <t>voor zijn doen nog daar naar / dat ik u zeggen dat zijn waar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6832,31 +6832,31 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="n">
-        <v>0.6708969173423673</v>
+        <v>0.6658833785784575</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dit was naer Noe VIIIc iaer / Ende XLVII daer naer</t>
+          <t>Danne ghesteente zelver of gout / Want vele beter es wijshede</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Voer sine doet noch daer naer / Dat ic u segghe dat es waer</t>
+          <t>Ende wijsheyden dan die here / Maer Wouter sijt seker des</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>dit zijn naar NOU-P achttiende jaar / en zevenenveertig daar naar</t>
+          <t>dan gesteente zelf of goud / want veel goed zijn wijsheid</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>voor zijn doen nog daar naar / dat ik u zeggen dat zijn waar</t>
+          <t>en wijsheid dan die heer / maar NOU-P zijn zeker de</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6872,31 +6872,31 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
-        <v>0.6721487845632599</v>
+        <v>0.6675190632087831</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Vriendelike bidden voir my / Omme dat ic die pine bestoet</t>
+          <t>Te sayene dat goede sait / Daer men ginder af ontfaet</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Maer ic biddu dat ghi / Claerlike betoent mi</t>
+          <t>Sine waren werdech wel daer ave / Ende sine mochtent te rechte wel ontfaen</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>vriendelijk bidden voor ik / om dat ik die pijn bestaan</t>
+          <t>te NOU-P dat goed zaad / daar men ginder af ontvangen</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>maar ik bidden du dat gij / klaarlijk betonen ik</t>
+          <t>zijn zijn waardig wel daar af / en zijn mogen het te rechte wel ontvangen</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6912,31 +6912,31 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="n">
-        <v>0.6770471347647078</v>
+        <v>0.6724100635938566</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Int latijn dichte als een clerc / Uten Grixe dat hy conste wale</t>
+          <t>In weet wat sire inne menen / Dese slachten wel den genen</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Alsic hem van dien ende van desen / Dichte ende ict hem soude senden</t>
+          <t>Ende wanen dat ic allene / Die goede metten quaden mene</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>in het latijn dichten als een klerk / uit dat griks dat hij kunnen wel</t>
+          <t>u weten wat zijn ik ne menen / deze slachten wel de geen</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>als ik hij van dat en van deze / dichten en ik het hij zullen zenden</t>
+          <t>en wanen dat ik alleen / die goed met de kwaad menen</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6952,31 +6952,31 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
-        <v>0.6771566563347095</v>
+        <v>0.6734140305887366</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Te sayene dat goede sait / Daer men ginder af ontfaet</t>
+          <t>Ende XLVII daer naer / Dese Sydrac was van Gode vercoren</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sine waren werdech wel daer ave / Ende sine mochtent te rechte wel ontfaen</t>
+          <t>NU beghint die kerstene wet vercoren / Daer Ihesus Cristus om wert gheboren</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>te NOU-P dat goed zaad / daar men ginder af ontvangen</t>
+          <t>en zevenenveertig daar naar / deze sidrac zijn van NOU-P verkiezen</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>zijn zijn waardig wel daar af / en zijn mogen het te rechte wel ontvangen</t>
+          <t>nu beginnen die kersten wet verkiezen / daar NOU-P NOU-P om worden geboren</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6992,7 +6992,7 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
-        <v>0.677857937214119</v>
+        <v>0.674530681680293</v>
       </c>
     </row>
     <row r="165">
@@ -7032,31 +7032,31 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="n">
-        <v>0.6795426401193581</v>
+        <v>0.6753480287027313</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>In weet wat sire inne menen / Dese slachten wel den genen</t>
+          <t>Vriendelike bidden voir my / Omme dat ic die pine bestoet</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ende wanen dat ic allene / Die goede metten quaden mene</t>
+          <t>Maer ic biddu dat ghi / Claerlike betoent mi</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>u weten wat zijn ik ne menen / deze slachten wel de geen</t>
+          <t>vriendelijk bidden voor ik / om dat ik die pijn bestaan</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>en wanen dat ik alleen / die goed met de kwaad menen</t>
+          <t>maar ik bidden du dat gij / klaarlijk betonen ik</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7072,31 +7072,31 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
-        <v>0.6802440503382158</v>
+        <v>0.6764586748378568</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ende XLVII daer naer / Dese Sydrac was van Gode vercoren</t>
+          <t>Ende oec zal hi doen verstaen / Hoet metten achtersten zal gaen</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NU beghint die kerstene wet vercoren / Daer Ihesus Cristus om wert gheboren</t>
+          <t>Alse Cristus selve doet verstaen / Ende hier na sal comen saen</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>en zevenenveertig daar naar / deze sidrac zijn van NOU-P verkiezen</t>
+          <t>en ook zullen hij doen verstaan / hoe het met de achterste zullen gaan</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>nu beginnen die kersten wet verkiezen / daar NOU-P NOU-P om worden geboren</t>
+          <t>als NOU-P zelf doen verstaan / en hier na zullen komen zaan</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7112,31 +7112,31 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="n">
-        <v>0.6807997571879173</v>
+        <v>0.6775612733407314</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ende oec zal hi doen verstaen / Hoet metten achtersten zal gaen</t>
+          <t>Daer na weder verhalen en can / Want die tijt es ons ghegeuen</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Alse Cristus selve doet verstaen / Ende hier na sal comen saen</t>
+          <t>Want clergye sonder goet leven / En can ghene salecheyt gheven</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>en ook zullen hij doen verstaan / hoe het met de achterste zullen gaan</t>
+          <t>daar na weder verhalen ne kunnen / want die tijd zijn ons geven</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>als NOU-P zelf doen verstaan / en hier na zullen komen zaan</t>
+          <t>want clergie zonder goed leven / ne kunnen gene zaligheid geven</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7152,31 +7152,31 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="n">
-        <v>0.6820825986269339</v>
+        <v>0.6775751523079379</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>34</v>
+        <v>172</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Daer na weder verhalen en can / Want die tijt es ons ghegeuen</t>
+          <t>Seker hy es herde sot / Ende vele meer dan ontsint</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Want clergye sonder goet leven / En can ghene salecheyt gheven</t>
+          <t>Ende menne soude houden over sot / Liete hijt onberecht bliven</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>daar na weder verhalen ne kunnen / want die tijd zijn ons geven</t>
+          <t>zeker hij zijn hard zot / en veel meer dan ontzinnen</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>want clergie zonder goed leven / ne kunnen gene zaligheid geven</t>
+          <t>en men zullen houden over zot / laten hij het onberecht blijven</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7192,31 +7192,31 @@
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="n">
-        <v>0.6838209873878285</v>
+        <v>0.6816653040837402</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Seker hy es herde sot / Ende vele meer dan ontsint</t>
+          <t>Int latijn dichte als een clerc / Uten Grixe dat hy conste wale</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ende menne soude houden over sot / Liete hijt onberecht bliven</t>
+          <t>Alsic hem van dien ende van desen / Dichte ende ict hem soude senden</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>zeker hij zijn hard zot / en veel meer dan ontzinnen</t>
+          <t>in het latijn dichten als een klerk / uit dat griks dat hij kunnen wel</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>en men zullen houden over zot / laten hij het onberecht blijven</t>
+          <t>als ik hij van dat en van deze / dichten en ik het hij zullen zenden</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7232,31 +7232,31 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
-        <v>0.6868098635649096</v>
+        <v>0.6836071817688829</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dat dese edele leringe soude / Den Dietscen lieden verholen wesen</t>
+          <t>Ende anders en hebben engene lere / Dan vechten ende vrouwen te minnen</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Soude een mensche voert ende weder / Sijn edel wesen al gronderen</t>
+          <t>Meer dan hen hadde ghemint / Ia die kindre van Ysrael</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>dat deze edel lering zullen / de Diets lieden verhelen wezen</t>
+          <t>en anders ne hebben negeen leer / dan vechten en vrouw te minnen</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>zullen een mens voort en weder / zijn edel wezen al gronderen</t>
+          <t>meer dan zij hebben minnen / ja die kind van NOU-P</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -7272,31 +7272,31 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
-        <v>0.6910599577959288</v>
+        <v>0.6879692906990721</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dien ghi droecht menschelike / O Maria reine vat</t>
+          <t>Dat dese edele leringe soude / Den Dietscen lieden verholen wesen</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Dat was Christus in waerre dinc / Die menschelike vorme ontfinc</t>
+          <t>Soude een mensche voert ende weder / Sijn edel wesen al gronderen</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>dat gij dragen menselijk / o NOU-P rein vat</t>
+          <t>dat deze edel lering zullen / de Diets lieden verhelen wezen</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>dat zijn NOU-P in waar ding / die menselijk vorm ontvangen</t>
+          <t>zullen een mens voort en weder / zijn edel wezen al gronderen</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -7312,31 +7312,31 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
-        <v>0.6914480599088949</v>
+        <v>0.6890116037184411</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ende anders en hebben engene lere / Dan vechten ende vrouwen te minnen</t>
+          <t>Daer men luttel orboers in vint / Nochtan half logene es ende mere</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Meer dan hen hadde ghemint / Ia die kindre van Ysrael</t>
+          <t>Daer men enen martelare vant / Men vonder dusent int lant</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>en anders ne hebben negeen leer / dan vechten en vrouw te minnen</t>
+          <t>daar men luttel oorbaar in vinden / nochtan half leugen zijn en meer</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>meer dan zij hebben minnen / ja die kind van NOU-P</t>
+          <t>daar men een martelaar vinden / men vinden er duizend in het land</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -7352,31 +7352,31 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
-        <v>0.6939037553116274</v>
+        <v>0.6898350164108105</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Come te ghenadighen vagheviere / Daerbeit zal mi wesen zwaer</t>
+          <t>Doet dicke die materie winden / Anders danse die makere seide</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ontfermhertich ende ghenadech / Waerwoerdech in hare spraken</t>
+          <t>Hi halet goet daer ment windt / Ende vueret daer mens niet en vindt</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>komen te genadig vagevuur / daarbeid zullen ik wezen zwaar</t>
+          <t>doen dik die materie winden / anders dans die maker zeggen</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ontfermhartig en genadig / waarwoordig in haar spraak</t>
+          <t>hij halen goed daar men het winden / en voeren daar men dat niet ne vinden</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -7392,31 +7392,31 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
-        <v>0.6951043631532262</v>
+        <v>0.6920421500829143</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Daer men luttel orboers in vint / Nochtan half logene es ende mere</t>
+          <t>Dien ghi droecht menschelike / O Maria reine vat</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Daer men enen martelare vant / Men vonder dusent int lant</t>
+          <t>Dat was Christus in waerre dinc / Die menschelike vorme ontfinc</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>daar men luttel oorbaar in vinden / nochtan half leugen zijn en meer</t>
+          <t>dat gij dragen menselijk / o NOU-P rein vat</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>daar men een martelaar vinden / men vinden er duizend in het land</t>
+          <t>dat zijn NOU-P in waar ding / die menselijk vorm ontvangen</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -7432,31 +7432,31 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
-        <v>0.6952464438722338</v>
+        <v>0.6924249846963442</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>137</v>
+        <v>66</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Macht sin ende ghesonde / Ende te levene zo langhe stonde</t>
+          <t>Ende ierstwerven int scrift leide / Die de materie sal leggen wale</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Dan datmen hem bidt om lanc leven / Want so die nideghe langher leeft</t>
+          <t>Ia die kindre van Ysrael / Die God leydde also wel</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>macht zin en gezonde / en te leven zo lang stonde</t>
+          <t>en eerstwerf in het schrift leiden / die de materie zullen leggen wel</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>dan dat men hij bidden om lang leven / want zo die nijdige lang leven</t>
+          <t>ja die kind van NOU-P / die NOU-P leiden alzo wel</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -7472,31 +7472,31 @@
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="n">
-        <v>0.6956345644375403</v>
+        <v>0.6927275636633816</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ende ierstwerven int scrift leide / Die de materie sal leggen wale</t>
+          <t>Doe men Gods iare noteerde / XIIIc XV ende drie</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ia die kindre van Ysrael / Die God leydde also wel</t>
+          <t>Wesen moesten emmer ene / Ende een moeten wesen drie</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>en eerstwerf in het schrift leiden / die de materie zullen leggen wel</t>
+          <t>toen men NOU-P jaar noteren / vierentwintig vijftien een drie</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>ja die kind van NOU-P / die NOU-P leiden alzo wel</t>
+          <t>wezen moeten immer een / en een moeten wezen drie</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -7512,31 +7512,31 @@
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="n">
-        <v>0.701172148342126</v>
+        <v>0.6951990342181527</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>64</v>
+        <v>197</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Doet dicke die materie winden / Anders danse die makere seide</t>
+          <t>Uten Walsce in Dietsce leide / Want ict niewer omme dede</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hi halet goet daer ment windt / Ende vueret daer mens niet en vindt</t>
+          <t>Maer dat si mesdoen dats mi leet / Die ghene diet ghelove souden</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>doen dik die materie winden / anders dans die maker zeggen</t>
+          <t>uit dat wals in Diets leed / want ik het niewer om doen</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>hij halen goed daar men het winden / en voeren daar men dat niet ne vinden</t>
+          <t>maar dat zij misdoen dat zijn ik leed / die gene die het geloven zullen</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7552,31 +7552,31 @@
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="n">
-        <v>0.7032010329768994</v>
+        <v>0.697335465355456</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>41</v>
+        <v>137</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Daer omme behoren sy ten vroeden / Die ghene die hem hier soe spoeden</t>
+          <t>Macht sin ende ghesonde / Ende te levene zo langhe stonde</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Die in alle verweenthede / Die der werelt toe behoert</t>
+          <t>Dan datmen hem bidt om lanc leven / Want so die nideghe langher leeft</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>daar om behoren zij ten vroed / die gene die hij hier zo spoeden</t>
+          <t>macht zin en gezonde / en te leven zo lang stonde</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>die in al verweendheid / die de wereld toezenden behoren</t>
+          <t>dan dat men hij bidden om lang leven / want zo die nijdige lang leven</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -7592,31 +7592,31 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
-        <v>0.7032822365317541</v>
+        <v>0.6979888474634717</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Met onoerboerliken saken / My dunct dat sy zere riesen</t>
+          <t>Come te ghenadighen vagheviere / Daerbeit zal mi wesen zwaer</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ende oec heeft groet wonder mi / Bi wat saken dat het si</t>
+          <t>Ontfermhertich ende ghenadech / Waerwoerdech in hare spraken</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>met onoorbaarlijk zaak / ik dunken dat zij zeer riezen</t>
+          <t>komen te genadig vagevuur / daarbeid zullen ik wezen zwaar</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>en ook hebben groot wonder ik / bij wat zaak dat het zij</t>
+          <t>ontfermhartig en genadig / waarwoordig in haar spraak</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7632,31 +7632,31 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="n">
-        <v>0.7044618642756482</v>
+        <v>0.6986116491056635</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Doe men Gods iare noteerde / XIIIc XV ende drie</t>
+          <t>Met onoerboerliken saken / My dunct dat sy zere riesen</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wesen moesten emmer ene / Ende een moeten wesen drie</t>
+          <t>Ende oec heeft groet wonder mi / Bi wat saken dat het si</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>toen men NOU-P jaar noteren / vierentwintig vijftien een drie</t>
+          <t>met onoorbaarlijk zaak / ik dunken dat zij zeer riezen</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>wezen moeten immer een / en een moeten wezen drie</t>
+          <t>en ook hebben groot wonder ik / bij wat zaak dat het zij</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7672,31 +7672,31 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
-        <v>0.7068573347235954</v>
+        <v>0.7030085887033791</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>197</v>
+        <v>41</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Uten Walsce in Dietsce leide / Want ict niewer omme dede</t>
+          <t>Daer omme behoren sy ten vroeden / Die ghene die hem hier soe spoeden</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Maer dat si mesdoen dats mi leet / Die ghene diet ghelove souden</t>
+          <t>Die in alle verweenthede / Die der werelt toe behoert</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>uit dat wals in Diets leed / want ik het niewer om doen</t>
+          <t>daar om behoren zij ten vroed / die gene die hij hier zo spoeden</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>maar dat zij misdoen dat zijn ik leed / die gene die het geloven zullen</t>
+          <t>die in al verweendheid / die de wereld toezenden behoren</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7712,7 +7712,7 @@
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="n">
-        <v>0.7069570693758788</v>
+        <v>0.7039179403164615</v>
       </c>
     </row>
     <row r="183">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hi maecter af dan enen sot / Ende hi es diene meest bespot</t>
+          <t>Gheven ende can oec wel sijn tale / Ende wint den andren al sijn goet</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>hij maken er afhebben hij dan een zot / en hij zijn die hij meest bespotten</t>
+          <t>geven en kunnen ook wel zijn taal / en winnen de ander al zijn goed</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -7752,7 +7752,7 @@
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="n">
-        <v>0.7120120213880322</v>
+        <v>0.7069851425182065</v>
       </c>
     </row>
     <row r="184">
@@ -7792,31 +7792,31 @@
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="n">
-        <v>0.7121469373464611</v>
+        <v>0.7085877400748987</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>73</v>
+        <v>193</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Die de bybele ende menich ander werc / Int latijn dichte als een clerc</t>
+          <t>In sine glorie ewelike / Dat hi mi so langhe spaerde</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Onse werken cleyn ende groet / Alse een dief als ende als</t>
+          <t>Om dinc van soe cleynen prise / Dijn ziele es doch ewelike</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>die de bijbel en menig ander werk / in het latijn dichten als een klerk</t>
+          <t>in zijn glorie eeuwelijk / dat hij ik zo lang sparen</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>ons werk klein en groot / als een dief als en als</t>
+          <t>om ding van zo klein prijs / dijn ziel zijn doch eeuwelijk</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -7832,31 +7832,31 @@
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="n">
-        <v>0.7136723151705071</v>
+        <v>0.7099734820681455</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>In sine glorie ewelike / Dat hi mi so langhe spaerde</t>
+          <t>Die beter es menichfout / Danne ghesteente zelver of gout</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Om dinc van soe cleynen prise / Dijn ziele es doch ewelike</t>
+          <t>Die over den ghenen maken claghe / Ende tyen hem valscheyt menechfout</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>in zijn glorie eeuwelijk / dat hij ik zo lang sparen</t>
+          <t>die goed zijn menigvout / dan gesteente zelf of goud</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>om ding van zo klein prijs / dijn ziel zijn doch eeuwelijk</t>
+          <t>die over de gene maken klaag / en tijgen hij valsheid menigvout</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -7872,31 +7872,31 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="n">
-        <v>0.7152325782046798</v>
+        <v>0.7108111201312151</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Die beter es menichfout / Danne ghesteente zelver of gout</t>
+          <t>Die de bybele ende menich ander werc / Int latijn dichte als een clerc</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Die over den ghenen maken claghe / Ende tyen hem valscheyt menechfout</t>
+          <t>Onse werken cleyn ende groet / Alse een dief als ende als</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>die goed zijn menigvout / dan gesteente zelf of goud</t>
+          <t>die de bijbel en menig ander werk / in het latijn dichten als een klerk</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>die over de gene maken klaag / en tijgen hij valsheid menigvout</t>
+          <t>ons werk klein en groot / als een dief als en als</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -7912,7 +7912,7 @@
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="n">
-        <v>0.7176946922089567</v>
+        <v>0.7137555618547209</v>
       </c>
     </row>
     <row r="188">
@@ -7952,7 +7952,7 @@
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="n">
-        <v>0.7190789584705332</v>
+        <v>0.713865929913051</v>
       </c>
     </row>
     <row r="189">
@@ -7992,31 +7992,31 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="n">
-        <v>0.7194580636112868</v>
+        <v>0.7167712622765317</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ende mijn leven betren zoe / Dat ic daer naer sciere</t>
+          <t>Selen ginder luttel mayen / Daer omme behoren sy ten vroeden</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Waer bi so dunct u des / Dat tfolc so zere ghebetert es</t>
+          <t>Daer ic haer prijs om gheve / Hoefsch goedertieren ende vroet</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>en mijn leven beteren zo / dat ik daar naar schieren</t>
+          <t>zullen ginder luttel maaien / daar om behoren zij ten vroed</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>waar bij zo dunken u des / dat dat volk zo zeer beteren zijn</t>
+          <t>daar ik zij prijs om geven / hoefs goedertieren en vroed</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8032,31 +8032,31 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="n">
-        <v>0.7236970435888724</v>
+        <v>0.7212544835720756</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Selen ginder luttel mayen / Daer omme behoren sy ten vroeden</t>
+          <t>Die men sonder astronomie / Niet toe gebringen en can</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Daer ic haer prijs om gheve / Hoefsch goedertieren ende vroet</t>
+          <t>Want sonder dese so en can / Die werelt al niet ghestaen</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>zullen ginder luttel maaien / daar om behoren zij ten vroed</t>
+          <t>die men zonder astronomie / niet toegespreken gebrengen ne kunnen</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>daar ik zij prijs om geven / hoefs goedertieren en vroed</t>
+          <t>want zonder deze zo ne kunnen / die wereld al niet gestaan</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8072,31 +8072,31 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="n">
-        <v>0.724466281740582</v>
+        <v>0.7265990728314132</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Die men sonder astronomie / Niet toe gebringen en can</t>
+          <t>Ende mijn leven betren zoe / Dat ic daer naer sciere</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Want sonder dese so en can / Die werelt al niet ghestaen</t>
+          <t>Waer bi so dunct u des / Dat tfolc so zere ghebetert es</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>die men zonder astronomie / niet toegespreken gebrengen ne kunnen</t>
+          <t>en mijn leven beteren zo / dat ik daar naar schieren</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>want zonder deze zo ne kunnen / die wereld al niet gestaan</t>
+          <t>waar bij zo dunken u des / dat dat volk zo zeer beteren zijn</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8112,31 +8112,31 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="n">
-        <v>0.7259195829561396</v>
+        <v>0.7277748479608592</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Dese slachten wel den genen / Die liden doer enen bogaert</t>
+          <t>Sonder rime in slechte woert / Doen werdic daer toe becoert</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Ghi slacht hem die tallen stonden / Alle dinc willen ondergronden</t>
+          <t>Ende al dat daer toe hoerde / Sciep hi al met enen woerde</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>deze slachten wel de geen / die lijden door een boomgaard</t>
+          <t>zonder rijm in slecht woord / toen worden ik daar toe bekoren</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>gij slachten hij die te al stond / al ding willen ondergronden</t>
+          <t>en al dat daar toe hoeren / scheppen hij al met een woord</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8152,31 +8152,31 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="n">
-        <v>0.7306303236775055</v>
+        <v>0.7308715795411584</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>141</v>
+        <v>54</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Dat ic daer naer sciere / Come te ghenadighen vagheviere</t>
+          <t>Doen werdic daer toe becoert / Dat ic dit boec woude maken</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Ontfermhertich ende ghenadech / Waerwoerdech in hare spraken</t>
+          <t>Ic bids u berecht mi dat / Dan die ghene diene heeft ghemaect</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>dat ik daar naar schieren / komen te genadig vagevuur</t>
+          <t>toen worden ik daar toe bekoren / dat ik dit boek willen maken</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ontfermhartig en genadig / waarwoordig in haar spraak</t>
+          <t>ik bidden dat u berechten ik dat / dan die gene die hij hebben maken</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8192,31 +8192,31 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="n">
-        <v>0.7323586643981312</v>
+        <v>0.7345415202986116</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Doen werdic daer toe becoert / Dat ic dit boec woude maken</t>
+          <t>Dat ic daer naer sciere / Come te ghenadighen vagheviere</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Die hen selven ghemaect heeft / Ende daer toe algader dat leeft</t>
+          <t>Ontfermhertich ende ghenadech / Waerwoerdech in hare spraken</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>toen worden ik daar toe bekoren / dat ik dit boek willen maken</t>
+          <t>dat ik daar naar schieren / komen te genadig vagevuur</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>die zij zelf maken hebben / en daar toe algader dat leven</t>
+          <t>ontfermhartig en genadig / waarwoordig in haar spraak</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8232,31 +8232,31 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="n">
-        <v>0.7328327650737797</v>
+        <v>0.7356447133597217</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Sonder rime in slechte woert / Doen werdic daer toe becoert</t>
+          <t>Dese slachten wel den genen / Die liden doer enen bogaert</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Ende al dat daer toe hoerde / Sciep hi al met enen woerde</t>
+          <t>Ghi slacht hem die tallen stonden / Alle dinc willen ondergronden</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>zonder rijm in slecht woord / toen worden ik daar toe bekoren</t>
+          <t>deze slachten wel de geen / die lijden door een boomgaard</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>en al dat daar toe hoeren / scheppen hij al met een woord</t>
+          <t>gij slachten hij die te al stond / al ding willen ondergronden</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -8272,31 +8272,31 @@
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="n">
-        <v>0.7333754722617769</v>
+        <v>0.7364054826871915</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Die ghene die hem hier soe spoeden / Te sayene dat goede sait</t>
+          <t>O Maria reine vat / Wanen soe quam u dat</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Na dien dat tfolc es so goet / Dat en ghene miraclen en doet</t>
+          <t>Om datmen onder hem vant / Silveren vate tenen stonden</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>die gene die hij hier zo spoeden / te NOU-P dat goed zaad</t>
+          <t>o NOU-P rein vat / waan zo komen u dat</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>na die dat dat volk zijn zo goed / dat ne gene mirakel ne doen</t>
+          <t>om hij dat men onder hij vinden / zilveren vat te een stond</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -8312,31 +8312,31 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="n">
-        <v>0.7354281033275871</v>
+        <v>0.7376142331053936</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ende oerbare leringhe in menigher stede / Waer of wi ons zouden hoeden</t>
+          <t>Die ghene die hem hier soe spoeden / Te sayene dat goede sait</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Dan exemple ende leringhe mede / Tonser groter salichede</t>
+          <t>Na dien dat tfolc es so goet / Dat en ghene miraclen en doet</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>en oorbaar lering in menig stede / waar af wij ons zullen hoeden</t>
+          <t>die gene die hij hier zo spoeden / te NOU-P dat goed zaad</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>dan exempel en lering mede / te ons groot zaligheid</t>
+          <t>na die dat dat volk zijn zo goed / dat ne gene mirakel ne doen</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -8352,31 +8352,31 @@
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="n">
-        <v>0.7381306549890513</v>
+        <v>0.7382204972402538</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>O Maria reine vat / Wanen soe quam u dat</t>
+          <t>Was philosophe ende astronomijn / Die God alsoe hadde vercoren</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Om datmen onder hem vant / Silveren vate tenen stonden</t>
+          <t>NU beghint die kerstene wet vercoren / Daer Ihesus Cristus om wert gheboren</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>o NOU-P rein vat / waan zo komen u dat</t>
+          <t>zijn filosoof en astronomijn / die NOU-P alzo hebben verkiezen</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>om hij dat men onder hij vinden / zilveren vat te een stond</t>
+          <t>nu beginnen die kersten wet verkiezen / daar NOU-P NOU-P om worden geboren</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -8392,31 +8392,31 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="n">
-        <v>0.7394764524791823</v>
+        <v>0.741482767636011</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Hebbic al gelaten uut / Nu hulpt my Goids bruit</t>
+          <t>Ende oerbare leringhe in menigher stede / Waer of wi ons zouden hoeden</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>God weet al die waerheyt / IAn nu hebdi mi gheseyt</t>
+          <t>Dan exemple ende leringhe mede / Tonser groter salichede</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>hebben ik al laten uiten / nu helpen ik NOU-P bruid</t>
+          <t>en oorbaar lering in menig stede / waar af wij ons zullen hoeden</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>NOU-P weten al die waarheid / NOU-P nu hebben gij ik zeggen</t>
+          <t>dan exempel en lering mede / te ons groot zaligheid</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -8432,31 +8432,31 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="n">
-        <v>0.743880031126458</v>
+        <v>0.7437026834661069</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>189</v>
+        <v>65</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Daer die ingelen singen hoge / Hier met latic dese prologhe</t>
+          <t>Anders danse die makere seide / Ende ierstwerven int scrift leide</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Es hier boven met Onsen Here / Ende metten heylighen inglen fijn</t>
+          <t>Dan op die ghemeyne broescheyt / Ende die anders hier toe seyt</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>daar die engel zingen hoog / hier met latiek deze proloog</t>
+          <t>anders dans die maker zeggen / en eerstwerf in het schrift leiden</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>zijn hier boven met ons heer / en met de heilig engel fijn</t>
+          <t>dan op die gemeen broedsheid / en die anders hier toe zeggen</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -8472,31 +8472,31 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="n">
-        <v>0.7455389317773478</v>
+        <v>0.7478995843667776</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Was philosophe ende astronomijn / Die God alsoe hadde vercoren</t>
+          <t>Hebbic al gelaten uut / Nu hulpt my Goids bruit</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>NU beghint die kerstene wet vercoren / Daer Ihesus Cristus om wert gheboren</t>
+          <t>Wouter mi es lief dat ghi / Des nu hebt vermaent mi</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>zijn filosoof en astronomijn / die NOU-P alzo hebben verkiezen</t>
+          <t>hebben ik al laten uiten / nu helpen ik NOU-P bruid</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>nu beginnen die kersten wet verkiezen / daar NOU-P NOU-P om worden geboren</t>
+          <t>NOU-P ik zijn lief dat gij / des nu hebben vermanen ik</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -8512,31 +8512,31 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="n">
-        <v>0.7455772747812351</v>
+        <v>0.7491994098809183</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Die liden doer enen bogaert / Die met vruchten sijn bewaert</t>
+          <t>Daer die ingelen singen hoge / Hier met latic dese prologhe</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Die doer haren lande liden / Dat hen en ghescien ghene scade</t>
+          <t>Es hier boven met Onsen Here / Ende metten heylighen inglen fijn</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>die lijden door een boomgaard / die met vrucht zijn bewaren</t>
+          <t>daar die engel zingen hoog / hier met latiek deze proloog</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>die door haar land lijden / dat zij ne geschieden gene schade</t>
+          <t>zijn hier boven met ons heer / en met de heilig engel fijn</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -8552,31 +8552,31 @@
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="n">
-        <v>0.750792926463823</v>
+        <v>0.7515412407590433</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Anders danse die makere seide / Ende ierstwerven int scrift leide</t>
+          <t>Die liden doer enen bogaert / Die met vruchten sijn bewaert</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Dan op die ghemeyne broescheyt / Ende die anders hier toe seyt</t>
+          <t>Die doer haren lande liden / Dat hen en ghescien ghene scade</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>anders dans die maker zeggen / en eerstwerf in het schrift leiden</t>
+          <t>die lijden door een boomgaard / die met vrucht zijn bewaren</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>dan op die gemeen broedsheid / en die anders hier toe zeggen</t>
+          <t>die door haar land lijden / dat zij ne geschieden gene schade</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -8592,7 +8592,7 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="n">
-        <v>0.7520736379997034</v>
+        <v>0.7535060451628119</v>
       </c>
     </row>
     <row r="205">
@@ -8632,7 +8632,7 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="n">
-        <v>0.7579652836205195</v>
+        <v>0.7535416879660757</v>
       </c>
     </row>
     <row r="206">
@@ -8672,7 +8672,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="n">
-        <v>0.7593055251264553</v>
+        <v>0.7606261903460743</v>
       </c>
     </row>
     <row r="207">
@@ -8712,31 +8712,31 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="n">
-        <v>0.7714638329273364</v>
+        <v>0.7706933280678794</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Die goet sijn ende van smake soete / Ende van evelen geven boete</t>
+          <t>Sonder rime alsoe ic sach / Dat hy inden Walsce lach</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Ende oft gheest heeft ende leven / Ende quaet ende goet can gheven</t>
+          <t>Doen dat dietsche heere lach / Voer Damiaten die stede</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>die goed zijn en van smaak zoet / en van evelen geven boete</t>
+          <t>zonder rijm alzo ik zien / dat hij in de wals lachen</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>en of geesten hebben en leven / en kwaad en goed kunnen geven</t>
+          <t>toen dat Diets heer lachen / voor NOU-P die stede</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8752,31 +8752,31 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="n">
-        <v>0.7753078715061769</v>
+        <v>0.7768961680901713</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Sonder rime alsoe ic sach / Dat hy inden Walsce lach</t>
+          <t>Die goet sijn ende van smake soete / Ende van evelen geven boete</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Dats Gode sien ende met Hem leven / Met Hem in Hem sonder sneven</t>
+          <t>Ende oft gheest heeft ende leven / Ende quaet ende goet can gheven</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>zonder rijm alzo ik zien / dat hij in de wals lachen</t>
+          <t>die goed zijn en van smaak zoet / en van evelen geven boete</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>dat zijn NOU-P zien en met hij leven / met hij in hij zonder sneven</t>
+          <t>en of geesten hebben en leven / en kwaad en goed kunnen geven</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8792,7 +8792,7 @@
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="n">
-        <v>0.7760748082950313</v>
+        <v>0.7775508240296001</v>
       </c>
     </row>
     <row r="210">
@@ -8832,7 +8832,7 @@
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="n">
-        <v>0.7835443177098551</v>
+        <v>0.7872300518533083</v>
       </c>
     </row>
     <row r="211">
@@ -8872,7 +8872,7 @@
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="n">
-        <v>0.8266659616280932</v>
+        <v>0.8274270742043914</v>
       </c>
     </row>
     <row r="212">
@@ -8912,7 +8912,7 @@
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="n">
-        <v>0.8323196476817047</v>
+        <v>0.8364312400401879</v>
       </c>
     </row>
     <row r="213">
@@ -8952,7 +8952,7 @@
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="n">
-        <v>0.8386111459662248</v>
+        <v>0.8421847979840914</v>
       </c>
     </row>
   </sheetData>
